--- a/research/traditional_assets/database/data/hong_kong/hong_kong_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_office_equipment_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08522807086267076</v>
+        <v>0.08512501954574736</v>
       </c>
       <c r="C2">
-        <v>22.3254102445246</v>
+        <v>22.15243141906096</v>
       </c>
       <c r="D2">
-        <v>17.9054102445246</v>
+        <v>17.95233141906096</v>
       </c>
       <c r="E2">
-        <v>-18.1</v>
+        <v>-17.8801</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2199</v>
       </c>
       <c r="G2">
         <v>4.42</v>
@@ -1439,28 +1439,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01106097</v>
       </c>
       <c r="N2">
-        <v>2.832222222222222</v>
+        <v>2.821161252222222</v>
       </c>
       <c r="O2">
-        <v>0.4673166666666666</v>
+        <v>0.4654916066166666</v>
       </c>
       <c r="P2">
-        <v>2.364905555555555</v>
+        <v>2.355669645605555</v>
       </c>
       <c r="Q2">
-        <v>4.054905555555555</v>
+        <v>4.045669645605555</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08522807086267076</v>
+        <v>0.08556062075328016</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431575</v>
+        <v>0.7750085048859205</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>256.0555016623517</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08512501954574736</v>
+        <v>0.08502196822882395</v>
       </c>
       <c r="C3">
-        <v>22.15243141906096</v>
+        <v>21.9796991538311</v>
       </c>
       <c r="D3">
-        <v>17.95233141906096</v>
+        <v>17.9994991538311</v>
       </c>
       <c r="E3">
-        <v>-17.8801</v>
+        <v>-17.6602</v>
       </c>
       <c r="F3">
-        <v>0.2199</v>
+        <v>0.4398</v>
       </c>
       <c r="G3">
         <v>4.42</v>
@@ -1521,28 +1521,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M3">
-        <v>0.01106097</v>
+        <v>0.02212194</v>
       </c>
       <c r="N3">
-        <v>2.821161252222222</v>
+        <v>2.810100282222222</v>
       </c>
       <c r="O3">
-        <v>0.4654916066166666</v>
+        <v>0.4636665465666666</v>
       </c>
       <c r="P3">
-        <v>2.355669645605555</v>
+        <v>2.346433735655555</v>
       </c>
       <c r="Q3">
-        <v>4.045669645605555</v>
+        <v>4.036433735655556</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08556062075328016</v>
+        <v>0.08589995737635096</v>
       </c>
       <c r="T3">
-        <v>0.7750085048859205</v>
+        <v>0.7816228072764949</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>256.0555016623517</v>
+        <v>128.0277508311758</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08502196822882395</v>
+        <v>0.08491891691190055</v>
       </c>
       <c r="C4">
-        <v>21.9796991538311</v>
+        <v>21.80721539738255</v>
       </c>
       <c r="D4">
-        <v>17.9994991538311</v>
+        <v>18.04691539738255</v>
       </c>
       <c r="E4">
-        <v>-17.6602</v>
+        <v>-17.4403</v>
       </c>
       <c r="F4">
-        <v>0.4398</v>
+        <v>0.6597000000000001</v>
       </c>
       <c r="G4">
         <v>4.42</v>
@@ -1603,28 +1603,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M4">
-        <v>0.02212194</v>
+        <v>0.03318291</v>
       </c>
       <c r="N4">
-        <v>2.810100282222222</v>
+        <v>2.799039312222222</v>
       </c>
       <c r="O4">
-        <v>0.4636665465666666</v>
+        <v>0.4618414865166666</v>
       </c>
       <c r="P4">
-        <v>2.346433735655555</v>
+        <v>2.337197825705555</v>
       </c>
       <c r="Q4">
-        <v>4.036433735655556</v>
+        <v>4.027197825705556</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08589995737635096</v>
+        <v>0.08624629063082531</v>
       </c>
       <c r="T4">
-        <v>0.7816228072764949</v>
+        <v>0.7883734870359473</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>128.0277508311758</v>
+        <v>85.35183388745055</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08491891691190055</v>
+        <v>0.08481586559497714</v>
       </c>
       <c r="C5">
-        <v>21.80721539738255</v>
+        <v>21.63498211884945</v>
       </c>
       <c r="D5">
-        <v>18.04691539738255</v>
+        <v>18.09458211884945</v>
       </c>
       <c r="E5">
-        <v>-17.4403</v>
+        <v>-17.2204</v>
       </c>
       <c r="F5">
-        <v>0.6597000000000001</v>
+        <v>0.8796</v>
       </c>
       <c r="G5">
         <v>4.42</v>
@@ -1685,28 +1685,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M5">
-        <v>0.03318291</v>
+        <v>0.04424388</v>
       </c>
       <c r="N5">
-        <v>2.799039312222222</v>
+        <v>2.787978342222222</v>
       </c>
       <c r="O5">
-        <v>0.4618414865166666</v>
+        <v>0.4600164264666666</v>
       </c>
       <c r="P5">
-        <v>2.337197825705555</v>
+        <v>2.327961915755555</v>
       </c>
       <c r="Q5">
-        <v>4.027197825705556</v>
+        <v>4.017961915755556</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08624629063082531</v>
+        <v>0.08659983916143452</v>
       </c>
       <c r="T5">
-        <v>0.7883734870359473</v>
+        <v>0.795264805957055</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>85.35183388745055</v>
+        <v>64.01387541558792</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08481586559497714</v>
+        <v>0.08471281427805374</v>
       </c>
       <c r="C6">
-        <v>21.63498211884945</v>
+        <v>21.46300130822501</v>
       </c>
       <c r="D6">
-        <v>18.09458211884945</v>
+        <v>18.14250130822501</v>
       </c>
       <c r="E6">
-        <v>-17.2204</v>
+        <v>-17.0005</v>
       </c>
       <c r="F6">
-        <v>0.8796</v>
+        <v>1.0995</v>
       </c>
       <c r="G6">
         <v>4.42</v>
@@ -1767,28 +1767,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M6">
-        <v>0.04424388</v>
+        <v>0.05530485</v>
       </c>
       <c r="N6">
-        <v>2.787978342222222</v>
+        <v>2.776917372222222</v>
       </c>
       <c r="O6">
-        <v>0.4600164264666666</v>
+        <v>0.4581913664166666</v>
       </c>
       <c r="P6">
-        <v>2.327961915755555</v>
+        <v>2.318726005805555</v>
       </c>
       <c r="Q6">
-        <v>4.017961915755556</v>
+        <v>4.008726005805555</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08659983916143452</v>
+        <v>0.08696083081900394</v>
       </c>
       <c r="T6">
-        <v>0.795264805957055</v>
+        <v>0.8023012052765016</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>64.01387541558792</v>
+        <v>51.21110033247032</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08471281427805374</v>
+        <v>0.08460976296113032</v>
       </c>
       <c r="C7">
-        <v>21.46300130822501</v>
+        <v>21.29127497663855</v>
       </c>
       <c r="D7">
-        <v>18.14250130822501</v>
+        <v>18.19067497663855</v>
       </c>
       <c r="E7">
-        <v>-17.0005</v>
+        <v>-16.7806</v>
       </c>
       <c r="F7">
-        <v>1.0995</v>
+        <v>1.3194</v>
       </c>
       <c r="G7">
         <v>4.42</v>
@@ -1849,28 +1849,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M7">
-        <v>0.05530485</v>
+        <v>0.06636582000000001</v>
       </c>
       <c r="N7">
-        <v>2.776917372222222</v>
+        <v>2.765856402222222</v>
       </c>
       <c r="O7">
-        <v>0.4581913664166666</v>
+        <v>0.4563663063666666</v>
       </c>
       <c r="P7">
-        <v>2.318726005805555</v>
+        <v>2.309490095855555</v>
       </c>
       <c r="Q7">
-        <v>4.008726005805555</v>
+        <v>3.999490095855555</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08696083081900394</v>
+        <v>0.08732950315013864</v>
       </c>
       <c r="T7">
-        <v>0.8023012052765016</v>
+        <v>0.8094873152197662</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.21110033247032</v>
+        <v>42.67591694372527</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08460976296113032</v>
+        <v>0.08450671164420691</v>
       </c>
       <c r="C8">
-        <v>21.29127497663855</v>
+        <v>21.11980515663677</v>
       </c>
       <c r="D8">
-        <v>18.19067497663855</v>
+        <v>18.23910515663677</v>
       </c>
       <c r="E8">
-        <v>-16.7806</v>
+        <v>-16.5607</v>
       </c>
       <c r="F8">
-        <v>1.3194</v>
+        <v>1.5393</v>
       </c>
       <c r="G8">
         <v>4.42</v>
@@ -1931,28 +1931,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M8">
-        <v>0.06636582000000001</v>
+        <v>0.07742679</v>
       </c>
       <c r="N8">
-        <v>2.765856402222222</v>
+        <v>2.754795432222222</v>
       </c>
       <c r="O8">
-        <v>0.4563663063666666</v>
+        <v>0.4545412463166666</v>
       </c>
       <c r="P8">
-        <v>2.309490095855555</v>
+        <v>2.300254185905555</v>
       </c>
       <c r="Q8">
-        <v>3.999490095855555</v>
+        <v>3.990254185905556</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08732950315013864</v>
+        <v>0.08770610391850206</v>
       </c>
       <c r="T8">
-        <v>0.8094873152197662</v>
+        <v>0.8168279651618108</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.67591694372527</v>
+        <v>36.57935738033595</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08450671164420691</v>
+        <v>0.0844036603272835</v>
       </c>
       <c r="C9">
-        <v>21.11980515663677</v>
+        <v>20.9485939024697</v>
       </c>
       <c r="D9">
-        <v>18.23910515663677</v>
+        <v>18.2877939024697</v>
       </c>
       <c r="E9">
-        <v>-16.5607</v>
+        <v>-16.3408</v>
       </c>
       <c r="F9">
-        <v>1.5393</v>
+        <v>1.7592</v>
       </c>
       <c r="G9">
         <v>4.42</v>
@@ -2013,28 +2013,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M9">
-        <v>0.07742679000000001</v>
+        <v>0.08848776</v>
       </c>
       <c r="N9">
-        <v>2.754795432222222</v>
+        <v>2.743734462222222</v>
       </c>
       <c r="O9">
-        <v>0.4545412463166666</v>
+        <v>0.4527161862666666</v>
       </c>
       <c r="P9">
-        <v>2.300254185905555</v>
+        <v>2.291018275955555</v>
       </c>
       <c r="Q9">
-        <v>3.990254185905556</v>
+        <v>3.981018275955555</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08770610391850206</v>
+        <v>0.08809089166009076</v>
       </c>
       <c r="T9">
-        <v>0.8168279651618109</v>
+        <v>0.8243281944504215</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.57935738033594</v>
+        <v>32.00693770779395</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0844036603272835</v>
+        <v>0.0843006090103601</v>
       </c>
       <c r="C10">
-        <v>20.9485939024697</v>
+        <v>20.7776432903811</v>
       </c>
       <c r="D10">
-        <v>18.2877939024697</v>
+        <v>18.3367432903811</v>
       </c>
       <c r="E10">
-        <v>-16.3408</v>
+        <v>-16.1209</v>
       </c>
       <c r="F10">
-        <v>1.7592</v>
+        <v>1.9791</v>
       </c>
       <c r="G10">
         <v>4.42</v>
@@ -2095,28 +2095,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M10">
-        <v>0.08848776</v>
+        <v>0.09954873</v>
       </c>
       <c r="N10">
-        <v>2.743734462222222</v>
+        <v>2.732673492222222</v>
       </c>
       <c r="O10">
-        <v>0.4527161862666666</v>
+        <v>0.4508911262166666</v>
       </c>
       <c r="P10">
-        <v>2.291018275955555</v>
+        <v>2.281782366005555</v>
       </c>
       <c r="Q10">
-        <v>3.981018275955555</v>
+        <v>3.971782366005556</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08809089166009076</v>
+        <v>0.08848413627512099</v>
       </c>
       <c r="T10">
-        <v>0.8243281944504215</v>
+        <v>0.8319932639431775</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.00693770779395</v>
+        <v>28.45061129581685</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0843006090103601</v>
+        <v>0.0841975576934367</v>
       </c>
       <c r="C11">
-        <v>20.7776432903811</v>
+        <v>20.60695541890362</v>
       </c>
       <c r="D11">
-        <v>18.3367432903811</v>
+        <v>18.38595541890362</v>
       </c>
       <c r="E11">
-        <v>-16.1209</v>
+        <v>-15.901</v>
       </c>
       <c r="F11">
-        <v>1.9791</v>
+        <v>2.199</v>
       </c>
       <c r="G11">
         <v>4.42</v>
@@ -2177,28 +2177,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M11">
-        <v>0.09954873</v>
+        <v>0.1106097</v>
       </c>
       <c r="N11">
-        <v>2.732673492222222</v>
+        <v>2.721612522222222</v>
       </c>
       <c r="O11">
-        <v>0.4508911262166666</v>
+        <v>0.4490660661666666</v>
       </c>
       <c r="P11">
-        <v>2.281782366005555</v>
+        <v>2.272546456055555</v>
       </c>
       <c r="Q11">
-        <v>3.971782366005556</v>
+        <v>3.962546456055556</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08848413627512099</v>
+        <v>0.08888611965937411</v>
       </c>
       <c r="T11">
-        <v>0.8319932639431775</v>
+        <v>0.8398286683135505</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.45061129581685</v>
+        <v>25.60555016623517</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0841975576934367</v>
+        <v>0.08409450637651329</v>
       </c>
       <c r="C12">
-        <v>20.60695541890361</v>
+        <v>20.43653240915868</v>
       </c>
       <c r="D12">
-        <v>18.38595541890362</v>
+        <v>18.43543240915868</v>
       </c>
       <c r="E12">
-        <v>-15.901</v>
+        <v>-15.6811</v>
       </c>
       <c r="F12">
-        <v>2.199</v>
+        <v>2.4189</v>
       </c>
       <c r="G12">
         <v>4.42</v>
@@ -2259,28 +2259,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M12">
-        <v>0.1106097</v>
+        <v>0.12167067</v>
       </c>
       <c r="N12">
-        <v>2.721612522222222</v>
+        <v>2.710551552222222</v>
       </c>
       <c r="O12">
-        <v>0.4490660661666666</v>
+        <v>0.4472410061166666</v>
       </c>
       <c r="P12">
-        <v>2.272546456055555</v>
+        <v>2.263310546105555</v>
       </c>
       <c r="Q12">
-        <v>3.962546456055556</v>
+        <v>3.953310546105556</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08888611965937411</v>
+        <v>0.08929713637810482</v>
       </c>
       <c r="T12">
-        <v>0.8398286683135505</v>
+        <v>0.8478401491866283</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.60555016623517</v>
+        <v>23.27777287839561</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08409450637651329</v>
+        <v>0.08399145505958988</v>
       </c>
       <c r="C13">
-        <v>20.43653240915868</v>
+        <v>20.26637640516124</v>
       </c>
       <c r="D13">
-        <v>18.43543240915868</v>
+        <v>18.48517640516124</v>
       </c>
       <c r="E13">
-        <v>-15.6811</v>
+        <v>-15.4612</v>
       </c>
       <c r="F13">
-        <v>2.4189</v>
+        <v>2.6388</v>
       </c>
       <c r="G13">
         <v>4.42</v>
@@ -2341,28 +2341,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M13">
-        <v>0.12167067</v>
+        <v>0.13273164</v>
       </c>
       <c r="N13">
-        <v>2.710551552222222</v>
+        <v>2.699490582222222</v>
       </c>
       <c r="O13">
-        <v>0.4472410061166666</v>
+        <v>0.4454159460666666</v>
       </c>
       <c r="P13">
-        <v>2.263310546105555</v>
+        <v>2.254074636155555</v>
       </c>
       <c r="Q13">
-        <v>3.953310546105556</v>
+        <v>3.944074636155556</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08929713637810482</v>
+        <v>0.08971749438589759</v>
       </c>
       <c r="T13">
-        <v>0.8478401491866283</v>
+        <v>0.8560337091704578</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.27777287839561</v>
+        <v>21.33795847186264</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08399145505958988</v>
+        <v>0.08388840374266647</v>
       </c>
       <c r="C14">
-        <v>20.26637640516124</v>
+        <v>20.09648957412951</v>
       </c>
       <c r="D14">
-        <v>18.48517640516124</v>
+        <v>18.53518957412951</v>
       </c>
       <c r="E14">
-        <v>-15.4612</v>
+        <v>-15.2413</v>
       </c>
       <c r="F14">
-        <v>2.6388</v>
+        <v>2.8587</v>
       </c>
       <c r="G14">
         <v>4.42</v>
@@ -2423,28 +2423,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M14">
-        <v>0.13273164</v>
+        <v>0.14379261</v>
       </c>
       <c r="N14">
-        <v>2.699490582222222</v>
+        <v>2.688429612222222</v>
       </c>
       <c r="O14">
-        <v>0.4454159460666666</v>
+        <v>0.4435908860166666</v>
       </c>
       <c r="P14">
-        <v>2.254074636155555</v>
+        <v>2.244838726205555</v>
       </c>
       <c r="Q14">
-        <v>3.944074636155556</v>
+        <v>3.934838726205555</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08971749438589759</v>
+        <v>0.09014751579616836</v>
       </c>
       <c r="T14">
-        <v>0.8560337091704578</v>
+        <v>0.8644156268550652</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.33795847186264</v>
+        <v>19.69657705095012</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08388840374266647</v>
+        <v>0.08378535242574307</v>
       </c>
       <c r="C15">
-        <v>20.09648957412951</v>
+        <v>19.92687410679964</v>
       </c>
       <c r="D15">
-        <v>18.53518957412951</v>
+        <v>18.58547410679964</v>
       </c>
       <c r="E15">
-        <v>-15.2413</v>
+        <v>-15.0214</v>
       </c>
       <c r="F15">
-        <v>2.8587</v>
+        <v>3.078600000000001</v>
       </c>
       <c r="G15">
         <v>4.42</v>
@@ -2505,28 +2505,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M15">
-        <v>0.14379261</v>
+        <v>0.15485358</v>
       </c>
       <c r="N15">
-        <v>2.688429612222222</v>
+        <v>2.677368642222222</v>
       </c>
       <c r="O15">
-        <v>0.4435908860166666</v>
+        <v>0.4417658259666666</v>
       </c>
       <c r="P15">
-        <v>2.244838726205555</v>
+        <v>2.235602816255555</v>
       </c>
       <c r="Q15">
-        <v>3.934838726205555</v>
+        <v>3.925602816255555</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09014751579616836</v>
+        <v>0.09058753770435241</v>
       </c>
       <c r="T15">
-        <v>0.8644156268550652</v>
+        <v>0.8729924728579193</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.69657705095012</v>
+        <v>18.28967869016797</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08378535242574307</v>
+        <v>0.08368230110881968</v>
       </c>
       <c r="C16">
-        <v>19.92687410679964</v>
+        <v>19.75753221774569</v>
       </c>
       <c r="D16">
-        <v>18.58547410679964</v>
+        <v>18.63603221774569</v>
       </c>
       <c r="E16">
-        <v>-15.0214</v>
+        <v>-14.8015</v>
       </c>
       <c r="F16">
-        <v>3.078600000000001</v>
+        <v>3.298500000000001</v>
       </c>
       <c r="G16">
         <v>4.42</v>
@@ -2587,28 +2587,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M16">
-        <v>0.15485358</v>
+        <v>0.16591455</v>
       </c>
       <c r="N16">
-        <v>2.677368642222222</v>
+        <v>2.666307672222222</v>
       </c>
       <c r="O16">
-        <v>0.4417658259666666</v>
+        <v>0.4399407659166666</v>
       </c>
       <c r="P16">
-        <v>2.235602816255555</v>
+        <v>2.226366906305555</v>
       </c>
       <c r="Q16">
-        <v>3.925602816255555</v>
+        <v>3.916366906305556</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09058753770435241</v>
+        <v>0.09103791306919962</v>
       </c>
       <c r="T16">
-        <v>0.8729924728579193</v>
+        <v>0.881771127002017</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.28967869016797</v>
+        <v>17.07036677749011</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08368230110881968</v>
+        <v>0.08357924979189625</v>
       </c>
       <c r="C17">
-        <v>19.75753221774569</v>
+        <v>19.58846614570469</v>
       </c>
       <c r="D17">
-        <v>18.63603221774569</v>
+        <v>18.68686614570468</v>
       </c>
       <c r="E17">
-        <v>-14.8015</v>
+        <v>-14.5816</v>
       </c>
       <c r="F17">
-        <v>3.2985</v>
+        <v>3.5184</v>
       </c>
       <c r="G17">
         <v>4.42</v>
@@ -2669,28 +2669,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M17">
-        <v>0.16591455</v>
+        <v>0.17697552</v>
       </c>
       <c r="N17">
-        <v>2.666307672222222</v>
+        <v>2.655246702222222</v>
       </c>
       <c r="O17">
-        <v>0.4399407659166666</v>
+        <v>0.4381157058666666</v>
       </c>
       <c r="P17">
-        <v>2.226366906305555</v>
+        <v>2.217130996355555</v>
       </c>
       <c r="Q17">
-        <v>3.916366906305556</v>
+        <v>3.907130996355555</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09103791306919962</v>
+        <v>0.09149901165701935</v>
       </c>
       <c r="T17">
-        <v>0.881771127002017</v>
+        <v>0.890758796720974</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.07036677749011</v>
+        <v>16.00346885389698</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08357924979189625</v>
+        <v>0.08347619847497285</v>
       </c>
       <c r="C18">
-        <v>19.58846614570469</v>
+        <v>19.41967815390703</v>
       </c>
       <c r="D18">
-        <v>18.68686614570468</v>
+        <v>18.73797815390703</v>
       </c>
       <c r="E18">
-        <v>-14.5816</v>
+        <v>-14.3617</v>
       </c>
       <c r="F18">
-        <v>3.5184</v>
+        <v>3.738300000000001</v>
       </c>
       <c r="G18">
         <v>4.42</v>
@@ -2751,28 +2751,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M18">
-        <v>0.17697552</v>
+        <v>0.18803649</v>
       </c>
       <c r="N18">
-        <v>2.655246702222222</v>
+        <v>2.644185732222222</v>
       </c>
       <c r="O18">
-        <v>0.4381157058666666</v>
+        <v>0.4362906458166666</v>
       </c>
       <c r="P18">
-        <v>2.217130996355555</v>
+        <v>2.207895086405555</v>
       </c>
       <c r="Q18">
-        <v>3.907130996355555</v>
+        <v>3.897895086405556</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09149901165701935</v>
+        <v>0.09197122105418416</v>
       </c>
       <c r="T18">
-        <v>0.890758796720974</v>
+        <v>0.8999630367946049</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.00346885389698</v>
+        <v>15.06208833307951</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08347619847497285</v>
+        <v>0.08337314715804944</v>
       </c>
       <c r="C19">
-        <v>19.41967815390703</v>
+        <v>19.25117053041251</v>
       </c>
       <c r="D19">
-        <v>18.73797815390703</v>
+        <v>18.78937053041251</v>
       </c>
       <c r="E19">
-        <v>-14.3617</v>
+        <v>-14.1418</v>
       </c>
       <c r="F19">
-        <v>3.738300000000001</v>
+        <v>3.958200000000001</v>
       </c>
       <c r="G19">
         <v>4.42</v>
@@ -2833,28 +2833,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M19">
-        <v>0.18803649</v>
+        <v>0.19909746</v>
       </c>
       <c r="N19">
-        <v>2.644185732222222</v>
+        <v>2.633124762222222</v>
       </c>
       <c r="O19">
-        <v>0.4362906458166666</v>
+        <v>0.4344655857666666</v>
       </c>
       <c r="P19">
-        <v>2.207895086405555</v>
+        <v>2.198659176455555</v>
       </c>
       <c r="Q19">
-        <v>3.897895086405556</v>
+        <v>3.888659176455556</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09197122105418416</v>
+        <v>0.09245494775371883</v>
       </c>
       <c r="T19">
-        <v>0.8999630367946049</v>
+        <v>0.909391770528568</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.06208833307951</v>
+        <v>14.22530564790842</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08337314715804946</v>
+        <v>0.08327009584112605</v>
       </c>
       <c r="C20">
-        <v>19.2511705304125</v>
+        <v>19.08294558845161</v>
       </c>
       <c r="D20">
-        <v>18.7893705304125</v>
+        <v>18.84104558845161</v>
       </c>
       <c r="E20">
-        <v>-14.1418</v>
+        <v>-13.9219</v>
       </c>
       <c r="F20">
-        <v>3.9582</v>
+        <v>4.178100000000001</v>
       </c>
       <c r="G20">
         <v>4.42</v>
@@ -2915,28 +2915,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M20">
-        <v>0.19909746</v>
+        <v>0.21015843</v>
       </c>
       <c r="N20">
-        <v>2.633124762222222</v>
+        <v>2.622063792222222</v>
       </c>
       <c r="O20">
-        <v>0.4344655857666666</v>
+        <v>0.4326405257166666</v>
       </c>
       <c r="P20">
-        <v>2.198659176455555</v>
+        <v>2.189423266505555</v>
       </c>
       <c r="Q20">
-        <v>3.888659176455556</v>
+        <v>3.879423266505555</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09245494775371883</v>
+        <v>0.09295061832237782</v>
       </c>
       <c r="T20">
-        <v>0.909391770528568</v>
+        <v>0.9190533125028759</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.22530564790842</v>
+        <v>13.47660535065009</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08327009584112605</v>
+        <v>0.08341754452420262</v>
       </c>
       <c r="C21">
-        <v>19.08294558845161</v>
+        <v>18.78919474584768</v>
       </c>
       <c r="D21">
-        <v>18.84104558845161</v>
+        <v>18.76719474584769</v>
       </c>
       <c r="E21">
-        <v>-13.9219</v>
+        <v>-13.702</v>
       </c>
       <c r="F21">
-        <v>4.178100000000001</v>
+        <v>4.398000000000001</v>
       </c>
       <c r="G21">
         <v>4.42</v>
@@ -2997,45 +2997,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M21">
-        <v>0.21015843</v>
+        <v>0.2278164</v>
       </c>
       <c r="N21">
-        <v>2.622063792222222</v>
+        <v>2.604405822222222</v>
       </c>
       <c r="O21">
-        <v>0.4326405257166666</v>
+        <v>0.4297269606666666</v>
       </c>
       <c r="P21">
-        <v>2.189423266505555</v>
+        <v>2.174678861555555</v>
       </c>
       <c r="Q21">
-        <v>3.879423266505555</v>
+        <v>3.864678861555555</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09295061832237782</v>
+        <v>0.09345868065525328</v>
       </c>
       <c r="T21">
-        <v>0.9190533125028759</v>
+        <v>0.9289563930265416</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.165</v>
       </c>
       <c r="W21">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.47660535065009</v>
+        <v>12.43203835291147</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08341754452420262</v>
+        <v>0.08332701820727922</v>
       </c>
       <c r="C22">
-        <v>18.78919474584768</v>
+        <v>18.61456679517337</v>
       </c>
       <c r="D22">
-        <v>18.76719474584769</v>
+        <v>18.81246679517337</v>
       </c>
       <c r="E22">
-        <v>-13.702</v>
+        <v>-13.4821</v>
       </c>
       <c r="F22">
-        <v>4.398000000000001</v>
+        <v>4.617900000000001</v>
       </c>
       <c r="G22">
         <v>4.42</v>
@@ -3079,28 +3079,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M22">
-        <v>0.2278164</v>
+        <v>0.23920722</v>
       </c>
       <c r="N22">
-        <v>2.604405822222222</v>
+        <v>2.593015002222222</v>
       </c>
       <c r="O22">
-        <v>0.4297269606666666</v>
+        <v>0.4278474753666666</v>
       </c>
       <c r="P22">
-        <v>2.174678861555555</v>
+        <v>2.165167526855555</v>
       </c>
       <c r="Q22">
-        <v>3.864678861555555</v>
+        <v>3.855167526855555</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09345868065525328</v>
+        <v>0.0939796053256699</v>
       </c>
       <c r="T22">
-        <v>0.9289563930265416</v>
+        <v>0.9391101844495405</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.43203835291147</v>
+        <v>11.84003652658236</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08332701820727922</v>
+        <v>0.08323649189035583</v>
       </c>
       <c r="C23">
-        <v>18.61456679517337</v>
+        <v>18.44015779193125</v>
       </c>
       <c r="D23">
-        <v>18.81246679517337</v>
+        <v>18.85795779193125</v>
       </c>
       <c r="E23">
-        <v>-13.4821</v>
+        <v>-13.2622</v>
       </c>
       <c r="F23">
-        <v>4.617900000000001</v>
+        <v>4.837800000000001</v>
       </c>
       <c r="G23">
         <v>4.42</v>
@@ -3161,28 +3161,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M23">
-        <v>0.23920722</v>
+        <v>0.25059804</v>
       </c>
       <c r="N23">
-        <v>2.593015002222222</v>
+        <v>2.581624182222222</v>
       </c>
       <c r="O23">
-        <v>0.4278474753666666</v>
+        <v>0.4259679900666666</v>
       </c>
       <c r="P23">
-        <v>2.165167526855555</v>
+        <v>2.155656192155555</v>
       </c>
       <c r="Q23">
-        <v>3.855167526855555</v>
+        <v>3.845656192155555</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0939796053256699</v>
+        <v>0.09451388703891772</v>
       </c>
       <c r="T23">
-        <v>0.9391101844495405</v>
+        <v>0.9495243294987704</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.84003652658236</v>
+        <v>11.30185304810134</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08323649189035583</v>
+        <v>0.0831459655734324</v>
       </c>
       <c r="C24">
-        <v>18.44015779193125</v>
+        <v>18.26596932830174</v>
       </c>
       <c r="D24">
-        <v>18.85795779193125</v>
+        <v>18.90366932830174</v>
       </c>
       <c r="E24">
-        <v>-13.2622</v>
+        <v>-13.0423</v>
       </c>
       <c r="F24">
-        <v>4.837800000000001</v>
+        <v>5.057700000000001</v>
       </c>
       <c r="G24">
         <v>4.42</v>
@@ -3243,28 +3243,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M24">
-        <v>0.25059804</v>
+        <v>0.26198886</v>
       </c>
       <c r="N24">
-        <v>2.581624182222222</v>
+        <v>2.570233362222222</v>
       </c>
       <c r="O24">
-        <v>0.4259679900666666</v>
+        <v>0.4240885047666666</v>
       </c>
       <c r="P24">
-        <v>2.155656192155555</v>
+        <v>2.146144857455555</v>
       </c>
       <c r="Q24">
-        <v>3.845656192155555</v>
+        <v>3.836144857455555</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09451388703891772</v>
+        <v>0.09506204619926287</v>
       </c>
       <c r="T24">
-        <v>0.9495243294987704</v>
+        <v>0.960208971822006</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.30185304810134</v>
+        <v>10.8104681329665</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0831459655734324</v>
+        <v>0.083055439256509</v>
       </c>
       <c r="C25">
-        <v>18.26596932830174</v>
+        <v>18.09200301194043</v>
       </c>
       <c r="D25">
-        <v>18.90366932830174</v>
+        <v>18.94960301194043</v>
       </c>
       <c r="E25">
-        <v>-13.0423</v>
+        <v>-12.8224</v>
       </c>
       <c r="F25">
-        <v>5.057700000000001</v>
+        <v>5.277600000000001</v>
       </c>
       <c r="G25">
         <v>4.42</v>
@@ -3325,28 +3325,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M25">
-        <v>0.26198886</v>
+        <v>0.27337968</v>
       </c>
       <c r="N25">
-        <v>2.570233362222222</v>
+        <v>2.558842542222222</v>
       </c>
       <c r="O25">
-        <v>0.4240885047666666</v>
+        <v>0.4222090194666666</v>
       </c>
       <c r="P25">
-        <v>2.146144857455555</v>
+        <v>2.136633522755555</v>
       </c>
       <c r="Q25">
-        <v>3.836144857455555</v>
+        <v>3.826633522755555</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09506204619926287</v>
+        <v>0.09562463060066974</v>
       </c>
       <c r="T25">
-        <v>0.960208971822006</v>
+        <v>0.9711747889432216</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.8104681329665</v>
+        <v>10.36003196075956</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.083055439256509</v>
+        <v>0.08296491293958561</v>
       </c>
       <c r="C26">
-        <v>18.09200301194043</v>
+        <v>17.91826046616668</v>
       </c>
       <c r="D26">
-        <v>18.94960301194043</v>
+        <v>18.99576046616668</v>
       </c>
       <c r="E26">
-        <v>-12.8224</v>
+        <v>-12.6025</v>
       </c>
       <c r="F26">
-        <v>5.277600000000001</v>
+        <v>5.4975</v>
       </c>
       <c r="G26">
         <v>4.42</v>
@@ -3407,28 +3407,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M26">
-        <v>0.27337968</v>
+        <v>0.2847705</v>
       </c>
       <c r="N26">
-        <v>2.558842542222222</v>
+        <v>2.547451722222222</v>
       </c>
       <c r="O26">
-        <v>0.4222090194666666</v>
+        <v>0.4203295341666666</v>
       </c>
       <c r="P26">
-        <v>2.136633522755555</v>
+        <v>2.127122188055555</v>
       </c>
       <c r="Q26">
-        <v>3.826633522755555</v>
+        <v>3.817122188055555</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09562463060066974</v>
+        <v>0.0962022172527808</v>
       </c>
       <c r="T26">
-        <v>0.9711747889432216</v>
+        <v>0.9824330278543364</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.36003196075956</v>
+        <v>9.945630682329179</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08296491293958561</v>
+        <v>0.08324345662266218</v>
       </c>
       <c r="C27">
-        <v>17.91826046616668</v>
+        <v>17.55705008618739</v>
       </c>
       <c r="D27">
-        <v>18.99576046616668</v>
+        <v>18.85445008618739</v>
       </c>
       <c r="E27">
-        <v>-12.6025</v>
+        <v>-12.3826</v>
       </c>
       <c r="F27">
-        <v>5.4975</v>
+        <v>5.7174</v>
       </c>
       <c r="G27">
         <v>4.42</v>
@@ -3489,45 +3489,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M27">
-        <v>0.2847705</v>
+        <v>0.3058809</v>
       </c>
       <c r="N27">
-        <v>2.547451722222222</v>
+        <v>2.526341322222222</v>
       </c>
       <c r="O27">
-        <v>0.4203295341666666</v>
+        <v>0.4168463181666666</v>
       </c>
       <c r="P27">
-        <v>2.127122188055555</v>
+        <v>2.109495004055555</v>
       </c>
       <c r="Q27">
-        <v>3.817122188055555</v>
+        <v>3.799495004055555</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0962022172527808</v>
+        <v>0.0967954143549489</v>
       </c>
       <c r="T27">
-        <v>0.9824330278543364</v>
+        <v>0.9939955434927784</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.165</v>
       </c>
       <c r="W27">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.945630682329179</v>
+        <v>9.259232015540107</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08324345662266218</v>
+        <v>0.08316712530573878</v>
       </c>
       <c r="C28">
-        <v>17.55705008618739</v>
+        <v>17.37566482322348</v>
       </c>
       <c r="D28">
-        <v>18.85445008618739</v>
+        <v>18.89296482322348</v>
       </c>
       <c r="E28">
-        <v>-12.3826</v>
+        <v>-12.1627</v>
       </c>
       <c r="F28">
-        <v>5.7174</v>
+        <v>5.937300000000001</v>
       </c>
       <c r="G28">
         <v>4.42</v>
@@ -3571,28 +3571,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M28">
-        <v>0.3058809</v>
+        <v>0.3176455500000001</v>
       </c>
       <c r="N28">
-        <v>2.526341322222222</v>
+        <v>2.514576672222222</v>
       </c>
       <c r="O28">
-        <v>0.4168463181666666</v>
+        <v>0.4149051509166666</v>
       </c>
       <c r="P28">
-        <v>2.109495004055555</v>
+        <v>2.099671521305555</v>
       </c>
       <c r="Q28">
-        <v>3.799495004055555</v>
+        <v>3.789671521305555</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0967954143549489</v>
+        <v>0.09740486343251888</v>
       </c>
       <c r="T28">
-        <v>0.9939955434927784</v>
+        <v>1.005874840381589</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.259232015540107</v>
+        <v>8.916297496446028</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08316712530573878</v>
+        <v>0.08309079398881537</v>
       </c>
       <c r="C29">
-        <v>17.37566482322348</v>
+        <v>17.19443723352337</v>
       </c>
       <c r="D29">
-        <v>18.89296482322348</v>
+        <v>18.93163723352338</v>
       </c>
       <c r="E29">
-        <v>-12.1627</v>
+        <v>-11.9428</v>
       </c>
       <c r="F29">
-        <v>5.937300000000001</v>
+        <v>6.157200000000001</v>
       </c>
       <c r="G29">
         <v>4.42</v>
@@ -3653,28 +3653,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M29">
-        <v>0.3176455500000001</v>
+        <v>0.3294102</v>
       </c>
       <c r="N29">
-        <v>2.514576672222222</v>
+        <v>2.502812022222222</v>
       </c>
       <c r="O29">
-        <v>0.4149051509166666</v>
+        <v>0.4129639836666666</v>
       </c>
       <c r="P29">
-        <v>2.099671521305555</v>
+        <v>2.089848038555555</v>
       </c>
       <c r="Q29">
-        <v>3.789671521305555</v>
+        <v>3.779848038555556</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09740486343251888</v>
+        <v>0.09803124165113247</v>
       </c>
       <c r="T29">
-        <v>1.005874840381589</v>
+        <v>1.018084117739533</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.916297496446028</v>
+        <v>8.597858300144384</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08309079398881537</v>
+        <v>0.08301446267189196</v>
       </c>
       <c r="C30">
-        <v>17.19443723352337</v>
+        <v>17.01336828730728</v>
       </c>
       <c r="D30">
-        <v>18.93163723352338</v>
+        <v>18.97046828730728</v>
       </c>
       <c r="E30">
-        <v>-11.9428</v>
+        <v>-11.7229</v>
       </c>
       <c r="F30">
-        <v>6.157200000000001</v>
+        <v>6.377100000000001</v>
       </c>
       <c r="G30">
         <v>4.42</v>
@@ -3735,28 +3735,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M30">
-        <v>0.3294102</v>
+        <v>0.3411748500000001</v>
       </c>
       <c r="N30">
-        <v>2.502812022222222</v>
+        <v>2.491047372222222</v>
       </c>
       <c r="O30">
-        <v>0.4129639836666666</v>
+        <v>0.4110228164166665</v>
       </c>
       <c r="P30">
-        <v>2.089848038555555</v>
+        <v>2.080024555805555</v>
       </c>
       <c r="Q30">
-        <v>3.779848038555556</v>
+        <v>3.770024555805555</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09803124165113247</v>
+        <v>0.09867526432660841</v>
       </c>
       <c r="T30">
-        <v>1.018084117739533</v>
+        <v>1.030637318403334</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.597858300144384</v>
+        <v>8.301380427725611</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08301446267189196</v>
+        <v>0.08293813135496855</v>
       </c>
       <c r="C31">
-        <v>17.01336828730728</v>
+        <v>16.8324589627719</v>
       </c>
       <c r="D31">
-        <v>18.97046828730728</v>
+        <v>19.00945896277189</v>
       </c>
       <c r="E31">
-        <v>-11.7229</v>
+        <v>-11.503</v>
       </c>
       <c r="F31">
-        <v>6.3771</v>
+        <v>6.597</v>
       </c>
       <c r="G31">
         <v>4.42</v>
@@ -3817,28 +3817,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M31">
-        <v>0.34117485</v>
+        <v>0.3529395</v>
       </c>
       <c r="N31">
-        <v>2.491047372222222</v>
+        <v>2.479282722222222</v>
       </c>
       <c r="O31">
-        <v>0.4110228164166667</v>
+        <v>0.4090816491666666</v>
       </c>
       <c r="P31">
-        <v>2.080024555805555</v>
+        <v>2.070201073055555</v>
       </c>
       <c r="Q31">
-        <v>3.770024555805556</v>
+        <v>3.760201073055555</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09867526432660841</v>
+        <v>0.09933768764995508</v>
       </c>
       <c r="T31">
-        <v>1.030637318403334</v>
+        <v>1.043549181943245</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.301380427725611</v>
+        <v>8.024667746801425</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08293813135496855</v>
+        <v>0.08286180003804515</v>
       </c>
       <c r="C32">
-        <v>16.8324589627719</v>
+        <v>16.65171024617259</v>
       </c>
       <c r="D32">
-        <v>19.00945896277189</v>
+        <v>19.0486102461726</v>
       </c>
       <c r="E32">
-        <v>-11.503</v>
+        <v>-11.2831</v>
       </c>
       <c r="F32">
-        <v>6.597</v>
+        <v>6.8169</v>
       </c>
       <c r="G32">
         <v>4.42</v>
@@ -3899,28 +3899,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M32">
-        <v>0.3529395</v>
+        <v>0.36470415</v>
       </c>
       <c r="N32">
-        <v>2.479282722222222</v>
+        <v>2.467518072222222</v>
       </c>
       <c r="O32">
-        <v>0.4090816491666666</v>
+        <v>0.4071404819166666</v>
       </c>
       <c r="P32">
-        <v>2.070201073055555</v>
+        <v>2.060377590305555</v>
       </c>
       <c r="Q32">
-        <v>3.760201073055555</v>
+        <v>3.750377590305555</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09933768764995508</v>
+        <v>0.1000193116493408</v>
       </c>
       <c r="T32">
-        <v>1.043549181943245</v>
+        <v>1.056835302397355</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.024667746801425</v>
+        <v>7.765807496904605</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08286180003804515</v>
+        <v>0.08299922872112175</v>
       </c>
       <c r="C33">
-        <v>16.65171024617259</v>
+        <v>16.36143713601495</v>
       </c>
       <c r="D33">
-        <v>19.0486102461726</v>
+        <v>18.97823713601495</v>
       </c>
       <c r="E33">
-        <v>-11.2831</v>
+        <v>-11.0632</v>
       </c>
       <c r="F33">
-        <v>6.8169</v>
+        <v>7.0368</v>
       </c>
       <c r="G33">
         <v>4.42</v>
@@ -3981,45 +3981,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M33">
-        <v>0.36470415</v>
+        <v>0.38209824</v>
       </c>
       <c r="N33">
-        <v>2.467518072222222</v>
+        <v>2.450123982222222</v>
       </c>
       <c r="O33">
-        <v>0.4071404819166666</v>
+        <v>0.4042704570666666</v>
       </c>
       <c r="P33">
-        <v>2.060377590305555</v>
+        <v>2.045853525155555</v>
       </c>
       <c r="Q33">
-        <v>3.750377590305555</v>
+        <v>3.735853525155556</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1000193116493408</v>
+        <v>0.1007209834134143</v>
       </c>
       <c r="T33">
-        <v>1.056835302397355</v>
+        <v>1.070512191100116</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.165</v>
       </c>
       <c r="W33">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.765807496904605</v>
+        <v>7.412288060322449</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08299922872112175</v>
+        <v>0.08292957740419835</v>
       </c>
       <c r="C34">
-        <v>16.36143713601495</v>
+        <v>16.17713838175546</v>
       </c>
       <c r="D34">
-        <v>18.97823713601495</v>
+        <v>19.01383838175546</v>
       </c>
       <c r="E34">
-        <v>-11.0632</v>
+        <v>-10.8433</v>
       </c>
       <c r="F34">
-        <v>7.0368</v>
+        <v>7.256700000000001</v>
       </c>
       <c r="G34">
         <v>4.42</v>
@@ -4063,28 +4063,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M34">
-        <v>0.38209824</v>
+        <v>0.3940388100000001</v>
       </c>
       <c r="N34">
-        <v>2.450123982222222</v>
+        <v>2.438183412222222</v>
       </c>
       <c r="O34">
-        <v>0.4042704570666666</v>
+        <v>0.4023002630166666</v>
       </c>
       <c r="P34">
-        <v>2.045853525155555</v>
+        <v>2.035883149205555</v>
       </c>
       <c r="Q34">
-        <v>3.735853525155556</v>
+        <v>3.725883149205556</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1007209834134143</v>
+        <v>0.1014436006032811</v>
       </c>
       <c r="T34">
-        <v>1.070512191100116</v>
+        <v>1.084597345137287</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.412288060322449</v>
+        <v>7.187673270615707</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08292957740419835</v>
+        <v>0.08285992608727492</v>
       </c>
       <c r="C35">
-        <v>16.17713838175546</v>
+        <v>15.99297344717193</v>
       </c>
       <c r="D35">
-        <v>19.01383838175546</v>
+        <v>19.04957344717193</v>
       </c>
       <c r="E35">
-        <v>-10.8433</v>
+        <v>-10.6234</v>
       </c>
       <c r="F35">
-        <v>7.256700000000001</v>
+        <v>7.476600000000001</v>
       </c>
       <c r="G35">
         <v>4.42</v>
@@ -4145,28 +4145,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M35">
-        <v>0.3940388100000001</v>
+        <v>0.4059793800000001</v>
       </c>
       <c r="N35">
-        <v>2.438183412222222</v>
+        <v>2.426242842222222</v>
       </c>
       <c r="O35">
-        <v>0.4023002630166666</v>
+        <v>0.4003300689666666</v>
       </c>
       <c r="P35">
-        <v>2.035883149205555</v>
+        <v>2.025912773255555</v>
       </c>
       <c r="Q35">
-        <v>3.725883149205556</v>
+        <v>3.715912773255555</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1014436006032811</v>
+        <v>0.1021881152837499</v>
       </c>
       <c r="T35">
-        <v>1.084597345137287</v>
+        <v>1.09910932202407</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.187673270615707</v>
+        <v>6.976271115597598</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08285992608727492</v>
+        <v>0.08279027477035153</v>
       </c>
       <c r="C36">
-        <v>15.99297344717193</v>
+        <v>15.80894308819682</v>
       </c>
       <c r="D36">
-        <v>19.04957344717193</v>
+        <v>19.08544308819682</v>
       </c>
       <c r="E36">
-        <v>-10.6234</v>
+        <v>-10.4035</v>
       </c>
       <c r="F36">
-        <v>7.476600000000001</v>
+        <v>7.696500000000001</v>
       </c>
       <c r="G36">
         <v>4.42</v>
@@ -4227,28 +4227,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M36">
-        <v>0.4059793800000001</v>
+        <v>0.4179199500000001</v>
       </c>
       <c r="N36">
-        <v>2.426242842222222</v>
+        <v>2.414302272222222</v>
       </c>
       <c r="O36">
-        <v>0.4003300689666666</v>
+        <v>0.3983598749166666</v>
       </c>
       <c r="P36">
-        <v>2.025912773255555</v>
+        <v>2.015942397305555</v>
       </c>
       <c r="Q36">
-        <v>3.715912773255555</v>
+        <v>3.705942397305555</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1021881152837499</v>
+        <v>0.1029555381082331</v>
       </c>
       <c r="T36">
-        <v>1.09910932202407</v>
+        <v>1.1140678212766</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.976271115597598</v>
+        <v>6.776949083723381</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08279027477035153</v>
+        <v>0.08272062345342811</v>
       </c>
       <c r="C37">
-        <v>15.80894308819682</v>
+        <v>15.62504806646694</v>
       </c>
       <c r="D37">
-        <v>19.08544308819682</v>
+        <v>19.12144806646694</v>
       </c>
       <c r="E37">
-        <v>-10.4035</v>
+        <v>-10.1836</v>
       </c>
       <c r="F37">
-        <v>7.696500000000001</v>
+        <v>7.916400000000001</v>
       </c>
       <c r="G37">
         <v>4.42</v>
@@ -4309,28 +4309,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M37">
-        <v>0.4179199500000001</v>
+        <v>0.4298605200000001</v>
       </c>
       <c r="N37">
-        <v>2.414302272222222</v>
+        <v>2.402361702222222</v>
       </c>
       <c r="O37">
-        <v>0.3983598749166666</v>
+        <v>0.3963896808666666</v>
       </c>
       <c r="P37">
-        <v>2.015942397305555</v>
+        <v>2.005972021355555</v>
       </c>
       <c r="Q37">
-        <v>3.705942397305555</v>
+        <v>3.695972021355555</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1029555381082331</v>
+        <v>0.1037469428959814</v>
       </c>
       <c r="T37">
-        <v>1.1140678212766</v>
+        <v>1.129493773630772</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.776949083723381</v>
+        <v>6.588700498064398</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08272062345342812</v>
+        <v>0.08265097213650471</v>
       </c>
       <c r="C38">
-        <v>15.62504806646693</v>
+        <v>15.44128914937727</v>
       </c>
       <c r="D38">
-        <v>19.12144806646693</v>
+        <v>19.15758914937727</v>
       </c>
       <c r="E38">
-        <v>-10.1836</v>
+        <v>-9.963700000000001</v>
       </c>
       <c r="F38">
-        <v>7.9164</v>
+        <v>8.1363</v>
       </c>
       <c r="G38">
         <v>4.42</v>
@@ -4391,28 +4391,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M38">
-        <v>0.42986052</v>
+        <v>0.44180109</v>
       </c>
       <c r="N38">
-        <v>2.402361702222222</v>
+        <v>2.390421132222222</v>
       </c>
       <c r="O38">
-        <v>0.3963896808666666</v>
+        <v>0.3944194868166666</v>
       </c>
       <c r="P38">
-        <v>2.005972021355555</v>
+        <v>1.996001645405555</v>
       </c>
       <c r="Q38">
-        <v>3.695972021355555</v>
+        <v>3.686001645405555</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1037469428959814</v>
+        <v>0.1045634716452456</v>
       </c>
       <c r="T38">
-        <v>1.129493773630772</v>
+        <v>1.145409438758092</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.588700498064399</v>
+        <v>6.410627511630226</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08265097213650471</v>
+        <v>0.08258132081958131</v>
       </c>
       <c r="C39">
-        <v>15.44128914937727</v>
+        <v>15.25766711013559</v>
       </c>
       <c r="D39">
-        <v>19.15758914937727</v>
+        <v>19.19386711013559</v>
       </c>
       <c r="E39">
-        <v>-9.963700000000001</v>
+        <v>-9.7438</v>
       </c>
       <c r="F39">
-        <v>8.1363</v>
+        <v>8.356200000000001</v>
       </c>
       <c r="G39">
         <v>4.42</v>
@@ -4473,28 +4473,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M39">
-        <v>0.44180109</v>
+        <v>0.45374166</v>
       </c>
       <c r="N39">
-        <v>2.390421132222222</v>
+        <v>2.378480562222222</v>
       </c>
       <c r="O39">
-        <v>0.3944194868166666</v>
+        <v>0.3924492927666666</v>
       </c>
       <c r="P39">
-        <v>1.996001645405555</v>
+        <v>1.986031269455555</v>
       </c>
       <c r="Q39">
-        <v>3.686001645405555</v>
+        <v>3.676031269455556</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1045634716452456</v>
+        <v>0.1054063400315828</v>
       </c>
       <c r="T39">
-        <v>1.145409438758092</v>
+        <v>1.161838512437906</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.410627511630226</v>
+        <v>6.241926787639957</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08258132081958131</v>
+        <v>0.08283731950265789</v>
       </c>
       <c r="C40">
-        <v>15.25766711013559</v>
+        <v>14.90510079493453</v>
       </c>
       <c r="D40">
-        <v>19.19386711013559</v>
+        <v>19.06120079493453</v>
       </c>
       <c r="E40">
-        <v>-9.7438</v>
+        <v>-9.523900000000001</v>
       </c>
       <c r="F40">
-        <v>8.356200000000001</v>
+        <v>8.5761</v>
       </c>
       <c r="G40">
         <v>4.42</v>
@@ -4555,45 +4555,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M40">
-        <v>0.45374166</v>
+        <v>0.47425833</v>
       </c>
       <c r="N40">
-        <v>2.378480562222222</v>
+        <v>2.357963892222222</v>
       </c>
       <c r="O40">
-        <v>0.3924492927666666</v>
+        <v>0.3890640422166666</v>
       </c>
       <c r="P40">
-        <v>1.986031269455555</v>
+        <v>1.968899850005555</v>
       </c>
       <c r="Q40">
-        <v>3.676031269455556</v>
+        <v>3.658899850005556</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1054063400315828</v>
+        <v>0.1062768434469802</v>
       </c>
       <c r="T40">
-        <v>1.161838512437906</v>
+        <v>1.178806244271156</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.165</v>
       </c>
       <c r="W40">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.241926787639957</v>
+        <v>5.97189768332002</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08283731950265789</v>
+        <v>0.08277601818573449</v>
       </c>
       <c r="C41">
-        <v>14.90510079493453</v>
+        <v>14.71680172895078</v>
       </c>
       <c r="D41">
-        <v>19.06120079493453</v>
+        <v>19.09280172895078</v>
       </c>
       <c r="E41">
-        <v>-9.523900000000001</v>
+        <v>-9.304</v>
       </c>
       <c r="F41">
-        <v>8.5761</v>
+        <v>8.796000000000001</v>
       </c>
       <c r="G41">
         <v>4.42</v>
@@ -4637,28 +4637,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M41">
-        <v>0.47425833</v>
+        <v>0.4864188000000001</v>
       </c>
       <c r="N41">
-        <v>2.357963892222222</v>
+        <v>2.345803422222222</v>
       </c>
       <c r="O41">
-        <v>0.3890640422166666</v>
+        <v>0.3870575646666666</v>
       </c>
       <c r="P41">
-        <v>1.968899850005555</v>
+        <v>1.958745857555555</v>
       </c>
       <c r="Q41">
-        <v>3.658899850005556</v>
+        <v>3.648745857555555</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1062768434469802</v>
+        <v>0.1071763636428908</v>
       </c>
       <c r="T41">
-        <v>1.178806244271156</v>
+        <v>1.196339567165515</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.97189768332002</v>
+        <v>5.822600241237019</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08277601818573449</v>
+        <v>0.08271471686881109</v>
       </c>
       <c r="C42">
-        <v>14.71680172895078</v>
+        <v>14.52860761725276</v>
       </c>
       <c r="D42">
-        <v>19.09280172895078</v>
+        <v>19.12450761725276</v>
       </c>
       <c r="E42">
-        <v>-9.304</v>
+        <v>-9.084099999999999</v>
       </c>
       <c r="F42">
-        <v>8.796000000000001</v>
+        <v>9.015900000000002</v>
       </c>
       <c r="G42">
         <v>4.42</v>
@@ -4719,28 +4719,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M42">
-        <v>0.4864188000000001</v>
+        <v>0.4985792700000001</v>
       </c>
       <c r="N42">
-        <v>2.345803422222222</v>
+        <v>2.333642952222222</v>
       </c>
       <c r="O42">
-        <v>0.3870575646666666</v>
+        <v>0.3850510871166666</v>
       </c>
       <c r="P42">
-        <v>1.958745857555555</v>
+        <v>1.948591865105555</v>
       </c>
       <c r="Q42">
-        <v>3.648745857555555</v>
+        <v>3.638591865105556</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1071763636428908</v>
+        <v>0.1081063760488324</v>
       </c>
       <c r="T42">
-        <v>1.196339567165515</v>
+        <v>1.214467239988497</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.822600241237019</v>
+        <v>5.680585601206848</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08271471686881109</v>
+        <v>0.08265341555188768</v>
       </c>
       <c r="C43">
-        <v>14.52860761725276</v>
+        <v>14.34051898357778</v>
       </c>
       <c r="D43">
-        <v>19.12450761725276</v>
+        <v>19.15631898357778</v>
       </c>
       <c r="E43">
-        <v>-9.084099999999999</v>
+        <v>-8.8642</v>
       </c>
       <c r="F43">
-        <v>9.015900000000002</v>
+        <v>9.235800000000001</v>
       </c>
       <c r="G43">
         <v>4.42</v>
@@ -4801,28 +4801,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M43">
-        <v>0.4985792700000001</v>
+        <v>0.5107397400000001</v>
       </c>
       <c r="N43">
-        <v>2.333642952222222</v>
+        <v>2.321482482222222</v>
       </c>
       <c r="O43">
-        <v>0.3850510871166666</v>
+        <v>0.3830446095666666</v>
       </c>
       <c r="P43">
-        <v>1.948591865105555</v>
+        <v>1.938437872655555</v>
       </c>
       <c r="Q43">
-        <v>3.638591865105556</v>
+        <v>3.628437872655556</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1081063760488324</v>
+        <v>0.1090684578480822</v>
       </c>
       <c r="T43">
-        <v>1.214467239988497</v>
+        <v>1.233220004977787</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.680585601206848</v>
+        <v>5.545333563082875</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08265341555188768</v>
+        <v>0.08259211423496429</v>
       </c>
       <c r="C44">
-        <v>14.34051898357778</v>
+        <v>14.15253635515361</v>
       </c>
       <c r="D44">
-        <v>19.15631898357778</v>
+        <v>19.18823635515362</v>
       </c>
       <c r="E44">
-        <v>-8.8642</v>
+        <v>-8.644300000000001</v>
       </c>
       <c r="F44">
-        <v>9.235800000000001</v>
+        <v>9.4557</v>
       </c>
       <c r="G44">
         <v>4.42</v>
@@ -4883,28 +4883,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M44">
-        <v>0.5107397400000001</v>
+        <v>0.52290021</v>
       </c>
       <c r="N44">
-        <v>2.321482482222222</v>
+        <v>2.309322012222222</v>
       </c>
       <c r="O44">
-        <v>0.3830446095666666</v>
+        <v>0.3810381320166666</v>
       </c>
       <c r="P44">
-        <v>1.938437872655555</v>
+        <v>1.928283880205555</v>
       </c>
       <c r="Q44">
-        <v>3.628437872655556</v>
+        <v>3.618283880205555</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1090684578480822</v>
+        <v>0.1100642969034461</v>
       </c>
       <c r="T44">
-        <v>1.233220004977787</v>
+        <v>1.252630761721089</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.545333563082875</v>
+        <v>5.416372317429786</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08259211423496429</v>
+        <v>0.08253081291804086</v>
       </c>
       <c r="C45">
-        <v>14.15253635515361</v>
+        <v>13.96466026272772</v>
       </c>
       <c r="D45">
-        <v>19.18823635515362</v>
+        <v>19.22026026272772</v>
       </c>
       <c r="E45">
-        <v>-8.644300000000001</v>
+        <v>-8.4244</v>
       </c>
       <c r="F45">
-        <v>9.4557</v>
+        <v>9.675600000000001</v>
       </c>
       <c r="G45">
         <v>4.42</v>
@@ -4965,28 +4965,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M45">
-        <v>0.52290021</v>
+        <v>0.5350606800000001</v>
       </c>
       <c r="N45">
-        <v>2.309322012222222</v>
+        <v>2.297161542222222</v>
       </c>
       <c r="O45">
-        <v>0.3810381320166666</v>
+        <v>0.3790316544666666</v>
       </c>
       <c r="P45">
-        <v>1.928283880205555</v>
+        <v>1.918129887755555</v>
       </c>
       <c r="Q45">
-        <v>3.618283880205555</v>
+        <v>3.608129887755556</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1100642969034461</v>
+        <v>0.1110957016393587</v>
       </c>
       <c r="T45">
-        <v>1.252630761721089</v>
+        <v>1.27273475977665</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.416372317429786</v>
+        <v>5.293272946579108</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08253081291804086</v>
+        <v>0.08246951160111746</v>
       </c>
       <c r="C46">
-        <v>13.96466026272772</v>
+        <v>13.77689124059654</v>
       </c>
       <c r="D46">
-        <v>19.22026026272772</v>
+        <v>19.25239124059654</v>
       </c>
       <c r="E46">
-        <v>-8.4244</v>
+        <v>-8.204499999999999</v>
       </c>
       <c r="F46">
-        <v>9.675600000000001</v>
+        <v>9.895500000000002</v>
       </c>
       <c r="G46">
         <v>4.42</v>
@@ -5047,28 +5047,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M46">
-        <v>0.5350606800000001</v>
+        <v>0.5472211500000002</v>
       </c>
       <c r="N46">
-        <v>2.297161542222222</v>
+        <v>2.285001072222221</v>
       </c>
       <c r="O46">
-        <v>0.3790316544666666</v>
+        <v>0.3770251769166665</v>
       </c>
       <c r="P46">
-        <v>1.918129887755555</v>
+        <v>1.907975895305555</v>
       </c>
       <c r="Q46">
-        <v>3.608129887755556</v>
+        <v>3.597975895305555</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1110957016393587</v>
+        <v>0.1121646120020317</v>
       </c>
       <c r="T46">
-        <v>1.27273475977665</v>
+        <v>1.29356981230696</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.293272946579108</v>
+        <v>5.175644658877349</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08246951160111746</v>
+        <v>0.08240821028419407</v>
       </c>
       <c r="C47">
-        <v>13.77689124059654</v>
+        <v>13.58922982663533</v>
       </c>
       <c r="D47">
-        <v>19.25239124059654</v>
+        <v>19.28462982663532</v>
       </c>
       <c r="E47">
-        <v>-8.204499999999999</v>
+        <v>-7.9846</v>
       </c>
       <c r="F47">
-        <v>9.895500000000002</v>
+        <v>10.1154</v>
       </c>
       <c r="G47">
         <v>4.42</v>
@@ -5129,28 +5129,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M47">
-        <v>0.5472211500000002</v>
+        <v>0.55938162</v>
       </c>
       <c r="N47">
-        <v>2.285001072222221</v>
+        <v>2.272840602222222</v>
       </c>
       <c r="O47">
-        <v>0.3770251769166665</v>
+        <v>0.3750186993666666</v>
       </c>
       <c r="P47">
-        <v>1.907975895305555</v>
+        <v>1.897821902855555</v>
       </c>
       <c r="Q47">
-        <v>3.597975895305555</v>
+        <v>3.587821902855556</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1121646120020317</v>
+        <v>0.1132731116373964</v>
       </c>
       <c r="T47">
-        <v>1.29356981230696</v>
+        <v>1.315176533449504</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.175644658877349</v>
+        <v>5.06313064455393</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08240821028419407</v>
+        <v>0.08234690896727065</v>
       </c>
       <c r="C48">
-        <v>13.58922982663533</v>
+        <v>13.40167656232813</v>
       </c>
       <c r="D48">
-        <v>19.28462982663532</v>
+        <v>19.31697656232813</v>
       </c>
       <c r="E48">
-        <v>-7.9846</v>
+        <v>-7.764699999999999</v>
       </c>
       <c r="F48">
-        <v>10.1154</v>
+        <v>10.3353</v>
       </c>
       <c r="G48">
         <v>4.42</v>
@@ -5211,28 +5211,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M48">
-        <v>0.55938162</v>
+        <v>0.5715420900000001</v>
       </c>
       <c r="N48">
-        <v>2.272840602222222</v>
+        <v>2.260680132222221</v>
       </c>
       <c r="O48">
-        <v>0.3750186993666666</v>
+        <v>0.3730122218166665</v>
       </c>
       <c r="P48">
-        <v>1.897821902855555</v>
+        <v>1.887667910405555</v>
       </c>
       <c r="Q48">
-        <v>3.587821902855556</v>
+        <v>3.577667910405555</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1132731116373964</v>
+        <v>0.1144234414476805</v>
       </c>
       <c r="T48">
-        <v>1.315176533449504</v>
+        <v>1.33759860255969</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.06313064455393</v>
+        <v>4.95540446062725</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08234690896727065</v>
+        <v>0.08228560765034725</v>
       </c>
       <c r="C49">
-        <v>13.40167656232813</v>
+        <v>13.21423199279807</v>
       </c>
       <c r="D49">
-        <v>19.31697656232813</v>
+        <v>19.34943199279807</v>
       </c>
       <c r="E49">
-        <v>-7.764699999999999</v>
+        <v>-7.5448</v>
       </c>
       <c r="F49">
-        <v>10.3353</v>
+        <v>10.5552</v>
       </c>
       <c r="G49">
         <v>4.42</v>
@@ -5293,28 +5293,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M49">
-        <v>0.5715420900000001</v>
+        <v>0.5837025600000001</v>
       </c>
       <c r="N49">
-        <v>2.260680132222221</v>
+        <v>2.248519662222222</v>
       </c>
       <c r="O49">
-        <v>0.3730122218166665</v>
+        <v>0.3710057442666666</v>
       </c>
       <c r="P49">
-        <v>1.887667910405555</v>
+        <v>1.877513917955555</v>
       </c>
       <c r="Q49">
-        <v>3.577667910405555</v>
+        <v>3.567513917955556</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1144234414476805</v>
+        <v>0.1156180147122062</v>
       </c>
       <c r="T49">
-        <v>1.33759860255969</v>
+        <v>1.360883058943345</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.95540446062725</v>
+        <v>4.852166867697516</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08228560765034725</v>
+        <v>0.08222430633342383</v>
       </c>
       <c r="C50">
-        <v>13.21423199279807</v>
+        <v>13.02689666683799</v>
       </c>
       <c r="D50">
-        <v>19.34943199279807</v>
+        <v>19.381996666838</v>
       </c>
       <c r="E50">
-        <v>-7.5448</v>
+        <v>-7.324900000000001</v>
       </c>
       <c r="F50">
-        <v>10.5552</v>
+        <v>10.7751</v>
       </c>
       <c r="G50">
         <v>4.42</v>
@@ -5375,28 +5375,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M50">
-        <v>0.5837025600000001</v>
+        <v>0.5958630300000001</v>
       </c>
       <c r="N50">
-        <v>2.248519662222222</v>
+        <v>2.236359192222221</v>
       </c>
       <c r="O50">
-        <v>0.3710057442666666</v>
+        <v>0.3689992667166666</v>
       </c>
       <c r="P50">
-        <v>1.877513917955555</v>
+        <v>1.867359925505555</v>
       </c>
       <c r="Q50">
-        <v>3.567513917955556</v>
+        <v>3.557359925505555</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1156180147122062</v>
+        <v>0.1168594339871055</v>
       </c>
       <c r="T50">
-        <v>1.360883058943345</v>
+        <v>1.385080631263614</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.852166867697516</v>
+        <v>4.753143054071035</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08222430633342383</v>
+        <v>0.08216300501650042</v>
       </c>
       <c r="C51">
-        <v>13.02689666683799</v>
+        <v>12.83967113694142</v>
       </c>
       <c r="D51">
-        <v>19.381996666838</v>
+        <v>19.41467113694142</v>
       </c>
       <c r="E51">
-        <v>-7.324900000000001</v>
+        <v>-7.105</v>
       </c>
       <c r="F51">
-        <v>10.7751</v>
+        <v>10.995</v>
       </c>
       <c r="G51">
         <v>4.42</v>
@@ -5457,28 +5457,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M51">
-        <v>0.5958630300000001</v>
+        <v>0.6080235000000001</v>
       </c>
       <c r="N51">
-        <v>2.236359192222221</v>
+        <v>2.224198722222222</v>
       </c>
       <c r="O51">
-        <v>0.3689992667166666</v>
+        <v>0.3669927891666666</v>
       </c>
       <c r="P51">
-        <v>1.867359925505555</v>
+        <v>1.857205933055555</v>
       </c>
       <c r="Q51">
-        <v>3.557359925505555</v>
+        <v>3.547205933055555</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1168594339871055</v>
+        <v>0.1181505100330008</v>
       </c>
       <c r="T51">
-        <v>1.385080631263614</v>
+        <v>1.410246106476694</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.753143054071035</v>
+        <v>4.658080192989615</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08216300501650042</v>
+        <v>0.08210170369957703</v>
       </c>
       <c r="C52">
-        <v>12.83967113694142</v>
+        <v>12.65255595933373</v>
       </c>
       <c r="D52">
-        <v>19.41467113694142</v>
+        <v>19.44745595933373</v>
       </c>
       <c r="E52">
-        <v>-7.105</v>
+        <v>-6.8851</v>
       </c>
       <c r="F52">
-        <v>10.995</v>
+        <v>11.2149</v>
       </c>
       <c r="G52">
         <v>4.42</v>
@@ -5539,28 +5539,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M52">
-        <v>0.6080235000000001</v>
+        <v>0.6201839700000001</v>
       </c>
       <c r="N52">
-        <v>2.224198722222222</v>
+        <v>2.212038252222222</v>
       </c>
       <c r="O52">
-        <v>0.3669927891666666</v>
+        <v>0.3649863116166666</v>
       </c>
       <c r="P52">
-        <v>1.857205933055555</v>
+        <v>1.847051940605555</v>
       </c>
       <c r="Q52">
-        <v>3.547205933055555</v>
+        <v>3.537051940605555</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1181505100330008</v>
+        <v>0.1194942830603613</v>
       </c>
       <c r="T52">
-        <v>1.410246106476694</v>
+        <v>1.436438743943369</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.658080192989615</v>
+        <v>4.566745287244721</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08210170369957703</v>
+        <v>0.0831259023826536</v>
       </c>
       <c r="C53">
-        <v>12.65255595933373</v>
+        <v>11.89903031303199</v>
       </c>
       <c r="D53">
-        <v>19.44745595933373</v>
+        <v>18.91383031303199</v>
       </c>
       <c r="E53">
-        <v>-6.8851</v>
+        <v>-6.6652</v>
       </c>
       <c r="F53">
-        <v>11.2149</v>
+        <v>11.4348</v>
       </c>
       <c r="G53">
         <v>4.42</v>
@@ -5621,45 +5621,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M53">
-        <v>0.6201839700000001</v>
+        <v>0.6609314400000001</v>
       </c>
       <c r="N53">
-        <v>2.212038252222222</v>
+        <v>2.171290782222222</v>
       </c>
       <c r="O53">
-        <v>0.3649863116166666</v>
+        <v>0.3582629790666666</v>
       </c>
       <c r="P53">
-        <v>1.847051940605555</v>
+        <v>1.813027803155555</v>
       </c>
       <c r="Q53">
-        <v>3.537051940605555</v>
+        <v>3.503027803155555</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1194942830603613</v>
+        <v>0.1208940466305284</v>
       </c>
       <c r="T53">
-        <v>1.436438743943369</v>
+        <v>1.463722741304489</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.165</v>
       </c>
       <c r="W53">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.566745287244721</v>
+        <v>4.285198207884045</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0831259023826536</v>
+        <v>0.08308547606573022</v>
       </c>
       <c r="C54">
-        <v>11.89903031303199</v>
+        <v>11.69963739995028</v>
       </c>
       <c r="D54">
-        <v>18.91383031303199</v>
+        <v>18.93433739995028</v>
       </c>
       <c r="E54">
-        <v>-6.6652</v>
+        <v>-6.4453</v>
       </c>
       <c r="F54">
-        <v>11.4348</v>
+        <v>11.6547</v>
       </c>
       <c r="G54">
         <v>4.42</v>
@@ -5703,28 +5703,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M54">
-        <v>0.6609314400000001</v>
+        <v>0.6736416600000001</v>
       </c>
       <c r="N54">
-        <v>2.171290782222222</v>
+        <v>2.158580562222221</v>
       </c>
       <c r="O54">
-        <v>0.3582629790666666</v>
+        <v>0.3561657927666665</v>
       </c>
       <c r="P54">
-        <v>1.813027803155555</v>
+        <v>1.802414769455555</v>
       </c>
       <c r="Q54">
-        <v>3.503027803155555</v>
+        <v>3.492414769455555</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1208940466305284</v>
+        <v>0.1223533746079366</v>
       </c>
       <c r="T54">
-        <v>1.463722741304489</v>
+        <v>1.492167759829912</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.285198207884045</v>
+        <v>4.204345411508874</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08308547606573022</v>
+        <v>0.0830450497488068</v>
       </c>
       <c r="C55">
-        <v>11.69963739995028</v>
+        <v>11.50028900424743</v>
       </c>
       <c r="D55">
-        <v>18.93433739995028</v>
+        <v>18.95488900424743</v>
       </c>
       <c r="E55">
-        <v>-6.4453</v>
+        <v>-6.225399999999999</v>
       </c>
       <c r="F55">
-        <v>11.6547</v>
+        <v>11.8746</v>
       </c>
       <c r="G55">
         <v>4.42</v>
@@ -5785,28 +5785,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M55">
-        <v>0.6736416600000001</v>
+        <v>0.6863518800000002</v>
       </c>
       <c r="N55">
-        <v>2.158580562222221</v>
+        <v>2.145870342222222</v>
       </c>
       <c r="O55">
-        <v>0.3561657927666665</v>
+        <v>0.3540686064666666</v>
       </c>
       <c r="P55">
-        <v>1.802414769455555</v>
+        <v>1.791801735755555</v>
       </c>
       <c r="Q55">
-        <v>3.492414769455555</v>
+        <v>3.481801735755556</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1223533746079366</v>
+        <v>0.1238761516278409</v>
       </c>
       <c r="T55">
-        <v>1.492167759829912</v>
+        <v>1.521849518291222</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.204345411508874</v>
+        <v>4.126487163147599</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0830450497488068</v>
+        <v>0.0830046234318834</v>
       </c>
       <c r="C56">
-        <v>11.50028900424743</v>
+        <v>11.30098527104036</v>
       </c>
       <c r="D56">
-        <v>18.95488900424743</v>
+        <v>18.97548527104037</v>
       </c>
       <c r="E56">
-        <v>-6.225399999999999</v>
+        <v>-6.0055</v>
       </c>
       <c r="F56">
-        <v>11.8746</v>
+        <v>12.0945</v>
       </c>
       <c r="G56">
         <v>4.42</v>
@@ -5867,28 +5867,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M56">
-        <v>0.6863518800000002</v>
+        <v>0.6990621000000001</v>
       </c>
       <c r="N56">
-        <v>2.145870342222222</v>
+        <v>2.133160122222222</v>
       </c>
       <c r="O56">
-        <v>0.3540686064666666</v>
+        <v>0.3519714201666666</v>
       </c>
       <c r="P56">
-        <v>1.791801735755555</v>
+        <v>1.781188702055555</v>
       </c>
       <c r="Q56">
-        <v>3.481801735755556</v>
+        <v>3.471188702055556</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1238761516278409</v>
+        <v>0.1254666076264076</v>
       </c>
       <c r="T56">
-        <v>1.521849518291222</v>
+        <v>1.55285046601748</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.126487163147599</v>
+        <v>4.051460123817643</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0830046234318834</v>
+        <v>0.08460079711495998</v>
       </c>
       <c r="C57">
-        <v>11.30098527104036</v>
+        <v>10.30047836434452</v>
       </c>
       <c r="D57">
-        <v>18.97548527104037</v>
+        <v>18.19487836434453</v>
       </c>
       <c r="E57">
-        <v>-6.0055</v>
+        <v>-5.785599999999999</v>
       </c>
       <c r="F57">
-        <v>12.0945</v>
+        <v>12.3144</v>
       </c>
       <c r="G57">
         <v>4.42</v>
@@ -5949,45 +5949,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M57">
-        <v>0.6990621000000001</v>
+        <v>0.7548727200000002</v>
       </c>
       <c r="N57">
-        <v>2.133160122222222</v>
+        <v>2.077349502222221</v>
       </c>
       <c r="O57">
-        <v>0.3519714201666666</v>
+        <v>0.3427626678666665</v>
       </c>
       <c r="P57">
-        <v>1.781188702055555</v>
+        <v>1.734586834355555</v>
       </c>
       <c r="Q57">
-        <v>3.471188702055556</v>
+        <v>3.424586834355555</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1254666076264076</v>
+        <v>0.1271293570794545</v>
       </c>
       <c r="T57">
-        <v>1.55285046601748</v>
+        <v>1.585260547731295</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.165</v>
       </c>
       <c r="W57">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.051460123817643</v>
+        <v>3.751920220699221</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08460079711495998</v>
+        <v>0.08458959579803657</v>
       </c>
       <c r="C58">
-        <v>10.30047836434452</v>
+        <v>10.0858325206395</v>
       </c>
       <c r="D58">
-        <v>18.19487836434453</v>
+        <v>18.2001325206395</v>
       </c>
       <c r="E58">
-        <v>-5.785599999999999</v>
+        <v>-5.5657</v>
       </c>
       <c r="F58">
-        <v>12.3144</v>
+        <v>12.5343</v>
       </c>
       <c r="G58">
         <v>4.42</v>
@@ -6031,28 +6031,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M58">
-        <v>0.7548727200000002</v>
+        <v>0.7683525900000001</v>
       </c>
       <c r="N58">
-        <v>2.077349502222221</v>
+        <v>2.063869632222222</v>
       </c>
       <c r="O58">
-        <v>0.3427626678666665</v>
+        <v>0.3405384893166666</v>
       </c>
       <c r="P58">
-        <v>1.734586834355555</v>
+        <v>1.723331142905555</v>
       </c>
       <c r="Q58">
-        <v>3.424586834355555</v>
+        <v>3.413331142905555</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1271293570794545</v>
+        <v>0.1288694437163641</v>
       </c>
       <c r="T58">
-        <v>1.585260547731295</v>
+        <v>1.619178075106217</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.751920220699221</v>
+        <v>3.686097058932568</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08458959579803657</v>
+        <v>0.08457839448111315</v>
       </c>
       <c r="C59">
-        <v>10.0858325206395</v>
+        <v>9.871189712308722</v>
       </c>
       <c r="D59">
-        <v>18.2001325206395</v>
+        <v>18.20538971230872</v>
       </c>
       <c r="E59">
-        <v>-5.5657</v>
+        <v>-5.345799999999999</v>
       </c>
       <c r="F59">
-        <v>12.5343</v>
+        <v>12.7542</v>
       </c>
       <c r="G59">
         <v>4.42</v>
@@ -6113,28 +6113,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M59">
-        <v>0.7683525900000001</v>
+        <v>0.7818324600000002</v>
       </c>
       <c r="N59">
-        <v>2.063869632222222</v>
+        <v>2.050389762222221</v>
       </c>
       <c r="O59">
-        <v>0.3405384893166666</v>
+        <v>0.3383143107666665</v>
       </c>
       <c r="P59">
-        <v>1.723331142905555</v>
+        <v>1.712075451455555</v>
       </c>
       <c r="Q59">
-        <v>3.413331142905555</v>
+        <v>3.402075451455555</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1288694437163641</v>
+        <v>0.130692391621698</v>
       </c>
       <c r="T59">
-        <v>1.619178075106217</v>
+        <v>1.654710722832327</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.686097058932568</v>
+        <v>3.622543661364765</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08457839448111316</v>
+        <v>0.08456719316418977</v>
       </c>
       <c r="C60">
-        <v>9.871189712308716</v>
+        <v>9.656549941983272</v>
       </c>
       <c r="D60">
-        <v>18.20538971230872</v>
+        <v>18.21064994198327</v>
       </c>
       <c r="E60">
-        <v>-5.345800000000001</v>
+        <v>-5.125900000000001</v>
       </c>
       <c r="F60">
-        <v>12.7542</v>
+        <v>12.9741</v>
       </c>
       <c r="G60">
         <v>4.42</v>
@@ -6195,28 +6195,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M60">
-        <v>0.7818324600000001</v>
+        <v>0.79531233</v>
       </c>
       <c r="N60">
-        <v>2.050389762222222</v>
+        <v>2.036909892222222</v>
       </c>
       <c r="O60">
-        <v>0.3383143107666666</v>
+        <v>0.3360901322166666</v>
       </c>
       <c r="P60">
-        <v>1.712075451455555</v>
+        <v>1.700819760005555</v>
       </c>
       <c r="Q60">
-        <v>3.402075451455556</v>
+        <v>3.390819760005556</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.130692391621698</v>
+        <v>0.132604263815097</v>
       </c>
       <c r="T60">
-        <v>1.654710722832327</v>
+        <v>1.691976670447515</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.622543661364765</v>
+        <v>3.561144616256889</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08456719316418977</v>
+        <v>0.08455599184726637</v>
       </c>
       <c r="C61">
-        <v>9.656549941983272</v>
+        <v>9.441913212297324</v>
       </c>
       <c r="D61">
-        <v>18.21064994198327</v>
+        <v>18.21591321229732</v>
       </c>
       <c r="E61">
-        <v>-5.125900000000001</v>
+        <v>-4.906000000000001</v>
       </c>
       <c r="F61">
-        <v>12.9741</v>
+        <v>13.194</v>
       </c>
       <c r="G61">
         <v>4.42</v>
@@ -6277,28 +6277,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M61">
-        <v>0.79531233</v>
+        <v>0.8087922000000001</v>
       </c>
       <c r="N61">
-        <v>2.036909892222222</v>
+        <v>2.023430022222222</v>
       </c>
       <c r="O61">
-        <v>0.3360901322166666</v>
+        <v>0.3338659536666666</v>
       </c>
       <c r="P61">
-        <v>1.700819760005555</v>
+        <v>1.689564068555555</v>
       </c>
       <c r="Q61">
-        <v>3.390819760005556</v>
+        <v>3.379564068555555</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.132604263815097</v>
+        <v>0.1346117296181659</v>
       </c>
       <c r="T61">
-        <v>1.691976670447515</v>
+        <v>1.731105915443462</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.561144616256889</v>
+        <v>3.50179220598594</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08455599184726637</v>
+        <v>0.08597097053034294</v>
       </c>
       <c r="C62">
-        <v>9.441913212297324</v>
+        <v>8.580377510000698</v>
       </c>
       <c r="D62">
-        <v>18.21591321229732</v>
+        <v>17.5742775100007</v>
       </c>
       <c r="E62">
-        <v>-4.906000000000001</v>
+        <v>-4.6861</v>
       </c>
       <c r="F62">
-        <v>13.194</v>
+        <v>13.4139</v>
       </c>
       <c r="G62">
         <v>4.42</v>
@@ -6359,45 +6359,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M62">
-        <v>0.8087922000000001</v>
+        <v>0.8598309900000002</v>
       </c>
       <c r="N62">
-        <v>2.023430022222222</v>
+        <v>1.972391232222221</v>
       </c>
       <c r="O62">
-        <v>0.3338659536666666</v>
+        <v>0.3254445533166666</v>
       </c>
       <c r="P62">
-        <v>1.689564068555555</v>
+        <v>1.646946678905555</v>
       </c>
       <c r="Q62">
-        <v>3.379564068555555</v>
+        <v>3.336946678905555</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1346117296181659</v>
+        <v>0.1367221423854947</v>
       </c>
       <c r="T62">
-        <v>1.731105915443462</v>
+        <v>1.77224178838792</v>
       </c>
       <c r="U62">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V62">
         <v>0.165</v>
       </c>
       <c r="W62">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.50179220598594</v>
+        <v>3.293928987395792</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08597097053034294</v>
+        <v>0.08598314921341954</v>
       </c>
       <c r="C63">
-        <v>8.580377510000698</v>
+        <v>8.355151109251025</v>
       </c>
       <c r="D63">
-        <v>17.5742775100007</v>
+        <v>17.56895110925103</v>
       </c>
       <c r="E63">
-        <v>-4.6861</v>
+        <v>-4.466200000000001</v>
       </c>
       <c r="F63">
-        <v>13.4139</v>
+        <v>13.6338</v>
       </c>
       <c r="G63">
         <v>4.42</v>
@@ -6441,28 +6441,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M63">
-        <v>0.8598309900000002</v>
+        <v>0.8739265800000001</v>
       </c>
       <c r="N63">
-        <v>1.972391232222221</v>
+        <v>1.958295642222222</v>
       </c>
       <c r="O63">
-        <v>0.3254445533166666</v>
+        <v>0.3231187809666666</v>
       </c>
       <c r="P63">
-        <v>1.646946678905555</v>
+        <v>1.635176861255555</v>
       </c>
       <c r="Q63">
-        <v>3.336946678905555</v>
+        <v>3.325176861255556</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1367221423854947</v>
+        <v>0.1389436295089988</v>
       </c>
       <c r="T63">
-        <v>1.77224178838792</v>
+        <v>1.815542707276822</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.293928987395792</v>
+        <v>3.240801100502312</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08598314921341954</v>
+        <v>0.08599532789649614</v>
       </c>
       <c r="C64">
-        <v>8.355151109251025</v>
+        <v>8.129927936167357</v>
       </c>
       <c r="D64">
-        <v>17.56895110925103</v>
+        <v>17.56362793616736</v>
       </c>
       <c r="E64">
-        <v>-4.466200000000001</v>
+        <v>-4.2463</v>
       </c>
       <c r="F64">
-        <v>13.6338</v>
+        <v>13.8537</v>
       </c>
       <c r="G64">
         <v>4.42</v>
@@ -6523,28 +6523,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M64">
-        <v>0.8739265800000001</v>
+        <v>0.8880221700000002</v>
       </c>
       <c r="N64">
-        <v>1.958295642222222</v>
+        <v>1.944200052222222</v>
       </c>
       <c r="O64">
-        <v>0.3231187809666666</v>
+        <v>0.3207930086166666</v>
       </c>
       <c r="P64">
-        <v>1.635176861255555</v>
+        <v>1.623407043605555</v>
       </c>
       <c r="Q64">
-        <v>3.325176861255556</v>
+        <v>3.313407043605555</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1389436295089988</v>
+        <v>0.1412851970175571</v>
       </c>
       <c r="T64">
-        <v>1.815542707276822</v>
+        <v>1.861184216375936</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.240801100502312</v>
+        <v>3.189359813192751</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08599532789649614</v>
+        <v>0.08600750657957273</v>
       </c>
       <c r="C65">
-        <v>8.129927936167357</v>
+        <v>7.904707987816755</v>
       </c>
       <c r="D65">
-        <v>17.56362793616736</v>
+        <v>17.55830798781676</v>
       </c>
       <c r="E65">
-        <v>-4.2463</v>
+        <v>-4.026400000000001</v>
       </c>
       <c r="F65">
-        <v>13.8537</v>
+        <v>14.0736</v>
       </c>
       <c r="G65">
         <v>4.42</v>
@@ -6605,28 +6605,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M65">
-        <v>0.8880221700000002</v>
+        <v>0.9021177600000001</v>
       </c>
       <c r="N65">
-        <v>1.944200052222222</v>
+        <v>1.930104462222222</v>
       </c>
       <c r="O65">
-        <v>0.3207930086166666</v>
+        <v>0.3184672362666666</v>
       </c>
       <c r="P65">
-        <v>1.623407043605555</v>
+        <v>1.611637225955555</v>
       </c>
       <c r="Q65">
-        <v>3.313407043605555</v>
+        <v>3.301637225955556</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1412851970175571</v>
+        <v>0.1437568516099243</v>
       </c>
       <c r="T65">
-        <v>1.861184216375936</v>
+        <v>1.909361364869445</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.189359813192751</v>
+        <v>3.139526066111614</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08600750657957273</v>
+        <v>0.08601968526264933</v>
       </c>
       <c r="C66">
-        <v>7.904707987816755</v>
+        <v>7.679491261269831</v>
       </c>
       <c r="D66">
-        <v>17.55830798781676</v>
+        <v>17.55299126126983</v>
       </c>
       <c r="E66">
-        <v>-4.026400000000001</v>
+        <v>-3.8065</v>
       </c>
       <c r="F66">
-        <v>14.0736</v>
+        <v>14.2935</v>
       </c>
       <c r="G66">
         <v>4.42</v>
@@ -6687,28 +6687,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M66">
-        <v>0.9021177600000001</v>
+        <v>0.9162133500000001</v>
       </c>
       <c r="N66">
-        <v>1.930104462222222</v>
+        <v>1.916008872222222</v>
       </c>
       <c r="O66">
-        <v>0.3184672362666666</v>
+        <v>0.3161414639166666</v>
       </c>
       <c r="P66">
-        <v>1.611637225955555</v>
+        <v>1.599867408305555</v>
       </c>
       <c r="Q66">
-        <v>3.301637225955556</v>
+        <v>3.289867408305556</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1437568516099243</v>
+        <v>0.1463697436075695</v>
       </c>
       <c r="T66">
-        <v>1.909361364869445</v>
+        <v>1.960291493276868</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.139526066111614</v>
+        <v>3.091225665094512</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08601968526264933</v>
+        <v>0.08603186394572593</v>
       </c>
       <c r="C67">
-        <v>7.679491261269831</v>
+        <v>7.454277753600744</v>
       </c>
       <c r="D67">
-        <v>17.55299126126983</v>
+        <v>17.54767775360074</v>
       </c>
       <c r="E67">
-        <v>-3.8065</v>
+        <v>-3.586599999999999</v>
       </c>
       <c r="F67">
-        <v>14.2935</v>
+        <v>14.5134</v>
       </c>
       <c r="G67">
         <v>4.42</v>
@@ -6769,28 +6769,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M67">
-        <v>0.9162133500000001</v>
+        <v>0.9303089400000002</v>
       </c>
       <c r="N67">
-        <v>1.916008872222222</v>
+        <v>1.901913282222222</v>
       </c>
       <c r="O67">
-        <v>0.3161414639166666</v>
+        <v>0.3138156915666666</v>
       </c>
       <c r="P67">
-        <v>1.599867408305555</v>
+        <v>1.588097590655555</v>
       </c>
       <c r="Q67">
-        <v>3.289867408305556</v>
+        <v>3.278097590655555</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1463697436075695</v>
+        <v>0.149136335134488</v>
       </c>
       <c r="T67">
-        <v>1.960291493276868</v>
+        <v>2.014217511590611</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.091225665094512</v>
+        <v>3.04438891259308</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08603186394572593</v>
+        <v>0.09040775262880252</v>
       </c>
       <c r="C68">
-        <v>7.454277753600744</v>
+        <v>5.513002432695734</v>
       </c>
       <c r="D68">
-        <v>17.54767775360074</v>
+        <v>15.82630243269573</v>
       </c>
       <c r="E68">
-        <v>-3.586599999999999</v>
+        <v>-3.3667</v>
       </c>
       <c r="F68">
-        <v>14.5134</v>
+        <v>14.7333</v>
       </c>
       <c r="G68">
         <v>4.42</v>
@@ -6851,45 +6851,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M68">
-        <v>0.9303089400000002</v>
+        <v>1.05932427</v>
       </c>
       <c r="N68">
-        <v>1.901913282222222</v>
+        <v>1.772897952222221</v>
       </c>
       <c r="O68">
-        <v>0.3138156915666666</v>
+        <v>0.2925281621166665</v>
       </c>
       <c r="P68">
-        <v>1.588097590655555</v>
+        <v>1.480369790105555</v>
       </c>
       <c r="Q68">
-        <v>3.278097590655555</v>
+        <v>3.170369790105555</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.149136335134488</v>
+        <v>0.1520705988751591</v>
       </c>
       <c r="T68">
-        <v>2.014217511590611</v>
+        <v>2.07141177343852</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.165</v>
       </c>
       <c r="W68">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.04438891259308</v>
+        <v>2.673612134103395</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09040775262880252</v>
+        <v>0.09048506131187911</v>
       </c>
       <c r="C69">
-        <v>5.513002432695734</v>
+        <v>5.265721680311749</v>
       </c>
       <c r="D69">
-        <v>15.82630243269573</v>
+        <v>15.79892168031175</v>
       </c>
       <c r="E69">
-        <v>-3.3667</v>
+        <v>-3.146799999999999</v>
       </c>
       <c r="F69">
-        <v>14.7333</v>
+        <v>14.9532</v>
       </c>
       <c r="G69">
         <v>4.42</v>
@@ -6933,28 +6933,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M69">
-        <v>1.05932427</v>
+        <v>1.07513508</v>
       </c>
       <c r="N69">
-        <v>1.772897952222221</v>
+        <v>1.757087142222221</v>
       </c>
       <c r="O69">
-        <v>0.2925281621166665</v>
+        <v>0.2899193784666665</v>
       </c>
       <c r="P69">
-        <v>1.480369790105555</v>
+        <v>1.467167763755555</v>
       </c>
       <c r="Q69">
-        <v>3.170369790105555</v>
+        <v>3.157167763755555</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1520705988751591</v>
+        <v>0.1551882540996222</v>
       </c>
       <c r="T69">
-        <v>2.07141177343852</v>
+        <v>2.132180676651923</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.673612134103395</v>
+        <v>2.634294308601874</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09048506131187911</v>
+        <v>0.0905623699949557</v>
       </c>
       <c r="C70">
-        <v>5.265721680311749</v>
+        <v>5.018535506025787</v>
       </c>
       <c r="D70">
-        <v>15.79892168031175</v>
+        <v>15.77163550602579</v>
       </c>
       <c r="E70">
-        <v>-3.146799999999999</v>
+        <v>-2.926899999999998</v>
       </c>
       <c r="F70">
-        <v>14.9532</v>
+        <v>15.1731</v>
       </c>
       <c r="G70">
         <v>4.42</v>
@@ -7015,28 +7015,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M70">
-        <v>1.07513508</v>
+        <v>1.09094589</v>
       </c>
       <c r="N70">
-        <v>1.757087142222221</v>
+        <v>1.741276332222221</v>
       </c>
       <c r="O70">
-        <v>0.2899193784666665</v>
+        <v>0.2873105948166665</v>
       </c>
       <c r="P70">
-        <v>1.467167763755555</v>
+        <v>1.453965737405555</v>
       </c>
       <c r="Q70">
-        <v>3.157167763755555</v>
+        <v>3.143965737405555</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1551882540996222</v>
+        <v>0.1585070483708249</v>
       </c>
       <c r="T70">
-        <v>2.132180676651923</v>
+        <v>2.196870154266191</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.634294308601874</v>
+        <v>2.59611613021634</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0905623699949557</v>
+        <v>0.0906396786780323</v>
       </c>
       <c r="C71">
-        <v>5.018535506025787</v>
+        <v>4.77144342064779</v>
       </c>
       <c r="D71">
-        <v>15.77163550602579</v>
+        <v>15.74444342064779</v>
       </c>
       <c r="E71">
-        <v>-2.926899999999998</v>
+        <v>-2.706999999999999</v>
       </c>
       <c r="F71">
-        <v>15.1731</v>
+        <v>15.393</v>
       </c>
       <c r="G71">
         <v>4.42</v>
@@ -7097,28 +7097,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M71">
-        <v>1.09094589</v>
+        <v>1.1067567</v>
       </c>
       <c r="N71">
-        <v>1.741276332222221</v>
+        <v>1.725465522222221</v>
       </c>
       <c r="O71">
-        <v>0.2873105948166665</v>
+        <v>0.2847018111666665</v>
       </c>
       <c r="P71">
-        <v>1.453965737405555</v>
+        <v>1.440763711055555</v>
       </c>
       <c r="Q71">
-        <v>3.143965737405555</v>
+        <v>3.130763711055555</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1585070483708249</v>
+        <v>0.162047095593441</v>
       </c>
       <c r="T71">
-        <v>2.196870154266191</v>
+        <v>2.26587226372141</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.59611613021634</v>
+        <v>2.559028756927535</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0906396786780323</v>
+        <v>0.09071698736110889</v>
       </c>
       <c r="C72">
-        <v>4.77144342064779</v>
+        <v>4.524444938355586</v>
       </c>
       <c r="D72">
-        <v>15.74444342064779</v>
+        <v>15.71734493835559</v>
       </c>
       <c r="E72">
-        <v>-2.706999999999999</v>
+        <v>-2.487099999999998</v>
       </c>
       <c r="F72">
-        <v>15.393</v>
+        <v>15.6129</v>
       </c>
       <c r="G72">
         <v>4.42</v>
@@ -7179,28 +7179,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M72">
-        <v>1.1067567</v>
+        <v>1.12256751</v>
       </c>
       <c r="N72">
-        <v>1.725465522222221</v>
+        <v>1.709654712222221</v>
       </c>
       <c r="O72">
-        <v>0.2847018111666665</v>
+        <v>0.2820930275166665</v>
       </c>
       <c r="P72">
-        <v>1.440763711055555</v>
+        <v>1.427561684705555</v>
       </c>
       <c r="Q72">
-        <v>3.130763711055555</v>
+        <v>3.117561684705555</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.162047095593441</v>
+        <v>0.1658312840038238</v>
       </c>
       <c r="T72">
-        <v>2.26587226372141</v>
+        <v>2.339633139345955</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.559028756927535</v>
+        <v>2.52298609837926</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09071698736110889</v>
+        <v>0.09313897604418549</v>
       </c>
       <c r="C73">
-        <v>4.52444493835559</v>
+        <v>3.500403515161791</v>
       </c>
       <c r="D73">
-        <v>15.71734493835559</v>
+        <v>14.91320351516179</v>
       </c>
       <c r="E73">
-        <v>-2.487100000000002</v>
+        <v>-2.267200000000001</v>
       </c>
       <c r="F73">
-        <v>15.6129</v>
+        <v>15.8328</v>
       </c>
       <c r="G73">
         <v>4.42</v>
@@ -7261,45 +7261,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M73">
-        <v>1.12256751</v>
+        <v>1.20012624</v>
       </c>
       <c r="N73">
-        <v>1.709654712222222</v>
+        <v>1.632095982222222</v>
       </c>
       <c r="O73">
-        <v>0.2820930275166666</v>
+        <v>0.2692958370666666</v>
       </c>
       <c r="P73">
-        <v>1.427561684705555</v>
+        <v>1.362800145155555</v>
       </c>
       <c r="Q73">
-        <v>3.117561684705556</v>
+        <v>3.052800145155556</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1658312840038237</v>
+        <v>0.1698857715863767</v>
       </c>
       <c r="T73">
-        <v>2.339633139345954</v>
+        <v>2.41866264894368</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.165</v>
       </c>
       <c r="W73">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.522986098379261</v>
+        <v>2.359936919821219</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09313897604418549</v>
+        <v>0.09324884972726208</v>
       </c>
       <c r="C74">
-        <v>3.500403515161791</v>
+        <v>3.245970146995855</v>
       </c>
       <c r="D74">
-        <v>14.91320351516179</v>
+        <v>14.87867014699586</v>
       </c>
       <c r="E74">
-        <v>-2.267200000000001</v>
+        <v>-2.0473</v>
       </c>
       <c r="F74">
-        <v>15.8328</v>
+        <v>16.0527</v>
       </c>
       <c r="G74">
         <v>4.42</v>
@@ -7343,28 +7343,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M74">
-        <v>1.20012624</v>
+        <v>1.21679466</v>
       </c>
       <c r="N74">
-        <v>1.632095982222222</v>
+        <v>1.615427562222222</v>
       </c>
       <c r="O74">
-        <v>0.2692958370666666</v>
+        <v>0.2665455477666666</v>
       </c>
       <c r="P74">
-        <v>1.362800145155555</v>
+        <v>1.348882014455555</v>
       </c>
       <c r="Q74">
-        <v>3.052800145155556</v>
+        <v>3.038882014455556</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1698857715863767</v>
+        <v>0.1742405915824521</v>
       </c>
       <c r="T74">
-        <v>2.41866264894368</v>
+        <v>2.503546196289386</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.359936919821219</v>
+        <v>2.32760901680997</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09324884972726208</v>
+        <v>0.09335872341033866</v>
       </c>
       <c r="C75">
-        <v>3.245970146995855</v>
+        <v>2.991696341916459</v>
       </c>
       <c r="D75">
-        <v>14.87867014699586</v>
+        <v>14.84429634191646</v>
       </c>
       <c r="E75">
-        <v>-2.0473</v>
+        <v>-1.827400000000001</v>
       </c>
       <c r="F75">
-        <v>16.0527</v>
+        <v>16.2726</v>
       </c>
       <c r="G75">
         <v>4.42</v>
@@ -7425,28 +7425,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M75">
-        <v>1.21679466</v>
+        <v>1.23346308</v>
       </c>
       <c r="N75">
-        <v>1.615427562222222</v>
+        <v>1.598759142222222</v>
       </c>
       <c r="O75">
-        <v>0.2665455477666666</v>
+        <v>0.2637952584666666</v>
       </c>
       <c r="P75">
-        <v>1.348882014455555</v>
+        <v>1.334963883755555</v>
       </c>
       <c r="Q75">
-        <v>3.038882014455556</v>
+        <v>3.024963883755555</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1742405915824521</v>
+        <v>0.1789303977320718</v>
       </c>
       <c r="T75">
-        <v>2.503546196289386</v>
+        <v>2.594959247277069</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.32760901680997</v>
+        <v>2.296154840907132</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09335872341033866</v>
+        <v>0.09346859709341526</v>
       </c>
       <c r="C76">
-        <v>2.991696341916459</v>
+        <v>2.737580996569278</v>
       </c>
       <c r="D76">
-        <v>14.84429634191646</v>
+        <v>14.81008099656928</v>
       </c>
       <c r="E76">
-        <v>-1.827400000000001</v>
+        <v>-1.607500000000002</v>
       </c>
       <c r="F76">
-        <v>16.2726</v>
+        <v>16.4925</v>
       </c>
       <c r="G76">
         <v>4.42</v>
@@ -7507,28 +7507,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M76">
-        <v>1.23346308</v>
+        <v>1.2501315</v>
       </c>
       <c r="N76">
-        <v>1.598759142222222</v>
+        <v>1.582090722222222</v>
       </c>
       <c r="O76">
-        <v>0.2637952584666666</v>
+        <v>0.2610449691666666</v>
       </c>
       <c r="P76">
-        <v>1.334963883755555</v>
+        <v>1.321045753055555</v>
       </c>
       <c r="Q76">
-        <v>3.024963883755555</v>
+        <v>3.011045753055555</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1789303977320718</v>
+        <v>0.183995388373661</v>
       </c>
       <c r="T76">
-        <v>2.594959247277069</v>
+        <v>2.693685342343767</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.296154840907132</v>
+        <v>2.26553944302837</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09346859709341526</v>
+        <v>0.09357847077649185</v>
       </c>
       <c r="C77">
-        <v>2.737580996569278</v>
+        <v>2.483623017749316</v>
       </c>
       <c r="D77">
-        <v>14.81008099656928</v>
+        <v>14.77602301774932</v>
       </c>
       <c r="E77">
-        <v>-1.607500000000002</v>
+        <v>-1.387599999999999</v>
       </c>
       <c r="F77">
-        <v>16.4925</v>
+        <v>16.7124</v>
       </c>
       <c r="G77">
         <v>4.42</v>
@@ -7589,28 +7589,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M77">
-        <v>1.2501315</v>
+        <v>1.26679992</v>
       </c>
       <c r="N77">
-        <v>1.582090722222222</v>
+        <v>1.565422302222222</v>
       </c>
       <c r="O77">
-        <v>0.2610449691666666</v>
+        <v>0.2582946798666665</v>
       </c>
       <c r="P77">
-        <v>1.321045753055555</v>
+        <v>1.307127622355555</v>
       </c>
       <c r="Q77">
-        <v>3.011045753055555</v>
+        <v>2.997127622355555</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.183995388373661</v>
+        <v>0.1894824615687161</v>
       </c>
       <c r="T77">
-        <v>2.693685342343767</v>
+        <v>2.800638611999357</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.26553944302837</v>
+        <v>2.235729713514839</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09357847077649185</v>
+        <v>0.09368834445956845</v>
       </c>
       <c r="C78">
-        <v>2.483623017749316</v>
+        <v>2.229821322284455</v>
       </c>
       <c r="D78">
-        <v>14.77602301774932</v>
+        <v>14.74212132228446</v>
       </c>
       <c r="E78">
-        <v>-1.387599999999999</v>
+        <v>-1.1677</v>
       </c>
       <c r="F78">
-        <v>16.7124</v>
+        <v>16.9323</v>
       </c>
       <c r="G78">
         <v>4.42</v>
@@ -7671,28 +7671,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M78">
-        <v>1.26679992</v>
+        <v>1.28346834</v>
       </c>
       <c r="N78">
-        <v>1.565422302222222</v>
+        <v>1.548753882222222</v>
       </c>
       <c r="O78">
-        <v>0.2582946798666665</v>
+        <v>0.2555443905666666</v>
       </c>
       <c r="P78">
-        <v>1.307127622355555</v>
+        <v>1.293209491655555</v>
       </c>
       <c r="Q78">
-        <v>2.997127622355555</v>
+        <v>2.983209491655555</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1894824615687161</v>
+        <v>0.1954466715633411</v>
       </c>
       <c r="T78">
-        <v>2.800638611999357</v>
+        <v>2.916892165972823</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.235729713514839</v>
+        <v>2.206694262689971</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09368834445956845</v>
+        <v>0.09379821814264502</v>
       </c>
       <c r="C79">
-        <v>2.229821322284455</v>
+        <v>1.97617483692062</v>
       </c>
       <c r="D79">
-        <v>14.74212132228446</v>
+        <v>14.70837483692062</v>
       </c>
       <c r="E79">
-        <v>-1.1677</v>
+        <v>-0.9478000000000009</v>
       </c>
       <c r="F79">
-        <v>16.9323</v>
+        <v>17.1522</v>
       </c>
       <c r="G79">
         <v>4.42</v>
@@ -7753,28 +7753,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M79">
-        <v>1.28346834</v>
+        <v>1.30013676</v>
       </c>
       <c r="N79">
-        <v>1.548753882222222</v>
+        <v>1.532085462222222</v>
       </c>
       <c r="O79">
-        <v>0.2555443905666666</v>
+        <v>0.2527941012666666</v>
       </c>
       <c r="P79">
-        <v>1.293209491655555</v>
+        <v>1.279291360955555</v>
       </c>
       <c r="Q79">
-        <v>2.983209491655555</v>
+        <v>2.969291360955555</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1954466715633411</v>
+        <v>0.2019530824665683</v>
       </c>
       <c r="T79">
-        <v>2.916892165972823</v>
+        <v>3.043714224852969</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.206694262689971</v>
+        <v>2.178403310604202</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09379821814264502</v>
+        <v>0.09390809182572164</v>
       </c>
       <c r="C80">
-        <v>1.97617483692062</v>
+        <v>1.722682498208485</v>
       </c>
       <c r="D80">
-        <v>14.70837483692062</v>
+        <v>14.67478249820849</v>
       </c>
       <c r="E80">
-        <v>-0.9478000000000009</v>
+        <v>-0.7278999999999982</v>
       </c>
       <c r="F80">
-        <v>17.1522</v>
+        <v>17.3721</v>
       </c>
       <c r="G80">
         <v>4.42</v>
@@ -7835,28 +7835,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M80">
-        <v>1.30013676</v>
+        <v>1.31680518</v>
       </c>
       <c r="N80">
-        <v>1.532085462222222</v>
+        <v>1.515417042222222</v>
       </c>
       <c r="O80">
-        <v>0.2527941012666666</v>
+        <v>0.2500438119666666</v>
       </c>
       <c r="P80">
-        <v>1.279291360955555</v>
+        <v>1.265373230255555</v>
       </c>
       <c r="Q80">
-        <v>2.969291360955555</v>
+        <v>2.955373230255555</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2019530824665683</v>
+        <v>0.2090791515510554</v>
       </c>
       <c r="T80">
-        <v>3.043714224852969</v>
+        <v>3.182614575055034</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.178403310604202</v>
+        <v>2.150828585153516</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09390809182572164</v>
+        <v>0.09401796550879823</v>
       </c>
       <c r="C81">
-        <v>1.722682498208485</v>
+        <v>1.469343252391862</v>
       </c>
       <c r="D81">
-        <v>14.67478249820849</v>
+        <v>14.64134325239187</v>
       </c>
       <c r="E81">
-        <v>-0.7278999999999982</v>
+        <v>-0.5079999999999991</v>
       </c>
       <c r="F81">
-        <v>17.3721</v>
+        <v>17.592</v>
       </c>
       <c r="G81">
         <v>4.42</v>
@@ -7917,28 +7917,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M81">
-        <v>1.31680518</v>
+        <v>1.3334736</v>
       </c>
       <c r="N81">
-        <v>1.515417042222222</v>
+        <v>1.498748622222221</v>
       </c>
       <c r="O81">
-        <v>0.2500438119666666</v>
+        <v>0.2472935226666666</v>
       </c>
       <c r="P81">
-        <v>1.265373230255555</v>
+        <v>1.251455099555555</v>
       </c>
       <c r="Q81">
-        <v>2.955373230255555</v>
+        <v>2.941455099555555</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2090791515510554</v>
+        <v>0.2169178275439912</v>
       </c>
       <c r="T81">
-        <v>3.182614575055034</v>
+        <v>3.335404960277304</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.150828585153516</v>
+        <v>2.123943227839098</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09401796550879823</v>
+        <v>0.09412783919187483</v>
       </c>
       <c r="C82">
-        <v>1.469343252391862</v>
+        <v>1.216156055297411</v>
       </c>
       <c r="D82">
-        <v>14.64134325239187</v>
+        <v>14.60805605529741</v>
       </c>
       <c r="E82">
-        <v>-0.5079999999999991</v>
+        <v>-0.2881</v>
       </c>
       <c r="F82">
-        <v>17.592</v>
+        <v>17.8119</v>
       </c>
       <c r="G82">
         <v>4.42</v>
@@ -7999,28 +7999,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M82">
-        <v>1.3334736</v>
+        <v>1.35014202</v>
       </c>
       <c r="N82">
-        <v>1.498748622222221</v>
+        <v>1.482080202222221</v>
       </c>
       <c r="O82">
-        <v>0.2472935226666666</v>
+        <v>0.2445432333666666</v>
       </c>
       <c r="P82">
-        <v>1.251455099555555</v>
+        <v>1.237536968855555</v>
       </c>
       <c r="Q82">
-        <v>2.941455099555555</v>
+        <v>2.927536968855555</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2169178275439912</v>
+        <v>0.225581627325657</v>
       </c>
       <c r="T82">
-        <v>3.335404960277304</v>
+        <v>3.504278543944025</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.123943227839098</v>
+        <v>2.09772170650775</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09412783919187483</v>
+        <v>0.09423771287495142</v>
       </c>
       <c r="C83">
-        <v>1.216156055297411</v>
+        <v>0.9631198722259988</v>
       </c>
       <c r="D83">
-        <v>14.60805605529741</v>
+        <v>14.574919872226</v>
       </c>
       <c r="E83">
-        <v>-0.2881</v>
+        <v>-0.06819999999999737</v>
       </c>
       <c r="F83">
-        <v>17.8119</v>
+        <v>18.0318</v>
       </c>
       <c r="G83">
         <v>4.42</v>
@@ -8081,28 +8081,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M83">
-        <v>1.35014202</v>
+        <v>1.366810440000001</v>
       </c>
       <c r="N83">
-        <v>1.482080202222221</v>
+        <v>1.465411782222221</v>
       </c>
       <c r="O83">
-        <v>0.2445432333666666</v>
+        <v>0.2417929440666665</v>
       </c>
       <c r="P83">
-        <v>1.237536968855555</v>
+        <v>1.223618838155555</v>
       </c>
       <c r="Q83">
-        <v>2.927536968855555</v>
+        <v>2.913618838155555</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.225581627325657</v>
+        <v>0.2352080715275079</v>
       </c>
       <c r="T83">
-        <v>3.504278543944025</v>
+        <v>3.691915859129269</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.09772170650775</v>
+        <v>2.072139734477168</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09423771287495142</v>
+        <v>0.094347586558028</v>
       </c>
       <c r="C84">
-        <v>0.9631198722259988</v>
+        <v>0.7102336778454976</v>
       </c>
       <c r="D84">
-        <v>14.574919872226</v>
+        <v>14.5419336778455</v>
       </c>
       <c r="E84">
-        <v>-0.06819999999999737</v>
+        <v>0.1517000000000017</v>
       </c>
       <c r="F84">
-        <v>18.0318</v>
+        <v>18.2517</v>
       </c>
       <c r="G84">
         <v>4.42</v>
@@ -8163,28 +8163,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M84">
-        <v>1.366810440000001</v>
+        <v>1.38347886</v>
       </c>
       <c r="N84">
-        <v>1.465411782222221</v>
+        <v>1.448743362222221</v>
       </c>
       <c r="O84">
-        <v>0.2417929440666665</v>
+        <v>0.2390426547666666</v>
       </c>
       <c r="P84">
-        <v>1.223618838155555</v>
+        <v>1.209700707455555</v>
       </c>
       <c r="Q84">
-        <v>2.913618838155555</v>
+        <v>2.899700707455555</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2352080715275079</v>
+        <v>0.2459670385766354</v>
       </c>
       <c r="T84">
-        <v>3.691915859129269</v>
+        <v>3.901628152571602</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.072139734477168</v>
+        <v>2.047174195507564</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.094347586558028</v>
+        <v>0.0944574602411046</v>
       </c>
       <c r="C85">
-        <v>0.7102336778454976</v>
+        <v>0.4574964560849821</v>
       </c>
       <c r="D85">
-        <v>14.5419336778455</v>
+        <v>14.50909645608498</v>
       </c>
       <c r="E85">
-        <v>0.1517000000000017</v>
+        <v>0.3716000000000008</v>
       </c>
       <c r="F85">
-        <v>18.2517</v>
+        <v>18.4716</v>
       </c>
       <c r="G85">
         <v>4.42</v>
@@ -8245,28 +8245,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M85">
-        <v>1.38347886</v>
+        <v>1.40014728</v>
       </c>
       <c r="N85">
-        <v>1.448743362222221</v>
+        <v>1.432074942222221</v>
       </c>
       <c r="O85">
-        <v>0.2390426547666666</v>
+        <v>0.2362923654666665</v>
       </c>
       <c r="P85">
-        <v>1.209700707455555</v>
+        <v>1.195782576755555</v>
       </c>
       <c r="Q85">
-        <v>2.899700707455555</v>
+        <v>2.885782576755555</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2459670385766354</v>
+        <v>0.2580708765069039</v>
       </c>
       <c r="T85">
-        <v>3.901628152571602</v>
+        <v>4.137554482694227</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.047174195507564</v>
+        <v>2.022803074132473</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0944574602411046</v>
+        <v>0.1046457839241812</v>
       </c>
       <c r="C86">
-        <v>0.4574964560849821</v>
+        <v>-2.274450477201412</v>
       </c>
       <c r="D86">
-        <v>14.50909645608498</v>
+        <v>11.99704952279859</v>
       </c>
       <c r="E86">
-        <v>0.3716000000000008</v>
+        <v>0.5914999999999999</v>
       </c>
       <c r="F86">
-        <v>18.4716</v>
+        <v>18.6915</v>
       </c>
       <c r="G86">
         <v>4.42</v>
@@ -8327,45 +8327,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M86">
-        <v>1.40014728</v>
+        <v>1.682235</v>
       </c>
       <c r="N86">
-        <v>1.432074942222221</v>
+        <v>1.149987222222222</v>
       </c>
       <c r="O86">
-        <v>0.2362923654666665</v>
+        <v>0.1897478916666666</v>
       </c>
       <c r="P86">
-        <v>1.195782576755555</v>
+        <v>0.960239330555555</v>
       </c>
       <c r="Q86">
-        <v>2.885782576755555</v>
+        <v>2.650239330555555</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2580708765069037</v>
+        <v>0.2717885594945412</v>
       </c>
       <c r="T86">
-        <v>4.137554482694224</v>
+        <v>4.404937656833197</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.165</v>
       </c>
       <c r="W86">
-        <v>0.063293</v>
+        <v>0.07514999999999999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.022803074132473</v>
+        <v>1.68360676256422</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1046457839241812</v>
+        <v>0.1048742276072578</v>
       </c>
       <c r="C87">
-        <v>-2.274450477201412</v>
+        <v>-2.540743807932049</v>
       </c>
       <c r="D87">
-        <v>11.99704952279859</v>
+        <v>11.95065619206795</v>
       </c>
       <c r="E87">
-        <v>0.5914999999999999</v>
+        <v>0.811399999999999</v>
       </c>
       <c r="F87">
-        <v>18.6915</v>
+        <v>18.9114</v>
       </c>
       <c r="G87">
         <v>4.42</v>
@@ -8409,28 +8409,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M87">
-        <v>1.682235</v>
+        <v>1.702026</v>
       </c>
       <c r="N87">
-        <v>1.149987222222222</v>
+        <v>1.130196222222222</v>
       </c>
       <c r="O87">
-        <v>0.1897478916666666</v>
+        <v>0.1864823766666666</v>
       </c>
       <c r="P87">
-        <v>0.960239330555555</v>
+        <v>0.9437138455555552</v>
       </c>
       <c r="Q87">
-        <v>2.650239330555555</v>
+        <v>2.633713845555556</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2717885594945412</v>
+        <v>0.2874659114804127</v>
       </c>
       <c r="T87">
-        <v>4.404937656833197</v>
+        <v>4.710518427277739</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.68360676256422</v>
+        <v>1.664029939743706</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1048742276072578</v>
+        <v>0.1051026712903344</v>
       </c>
       <c r="C88">
-        <v>-2.540743807932049</v>
+        <v>-2.806679709119912</v>
       </c>
       <c r="D88">
-        <v>11.95065619206795</v>
+        <v>11.90462029088009</v>
       </c>
       <c r="E88">
-        <v>0.811399999999999</v>
+        <v>1.031300000000002</v>
       </c>
       <c r="F88">
-        <v>18.9114</v>
+        <v>19.1313</v>
       </c>
       <c r="G88">
         <v>4.42</v>
@@ -8491,28 +8491,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M88">
-        <v>1.702026</v>
+        <v>1.721817</v>
       </c>
       <c r="N88">
-        <v>1.130196222222222</v>
+        <v>1.110405222222222</v>
       </c>
       <c r="O88">
-        <v>0.1864823766666666</v>
+        <v>0.1832168616666666</v>
       </c>
       <c r="P88">
-        <v>0.9437138455555552</v>
+        <v>0.9271883605555551</v>
       </c>
       <c r="Q88">
-        <v>2.633713845555556</v>
+        <v>2.617188360555556</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2874659114804127</v>
+        <v>0.3055551637718029</v>
       </c>
       <c r="T88">
-        <v>4.710518427277739</v>
+        <v>5.063111623944517</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.664029939743706</v>
+        <v>1.644903158827112</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1051026712903344</v>
+        <v>0.105331114973411</v>
       </c>
       <c r="C89">
-        <v>-2.806679709119912</v>
+        <v>-3.072262295547052</v>
       </c>
       <c r="D89">
-        <v>11.90462029088009</v>
+        <v>11.85893770445295</v>
       </c>
       <c r="E89">
-        <v>1.031300000000002</v>
+        <v>1.251200000000001</v>
       </c>
       <c r="F89">
-        <v>19.1313</v>
+        <v>19.3512</v>
       </c>
       <c r="G89">
         <v>4.42</v>
@@ -8573,28 +8573,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M89">
-        <v>1.721817</v>
+        <v>1.741608</v>
       </c>
       <c r="N89">
-        <v>1.110405222222222</v>
+        <v>1.090614222222222</v>
       </c>
       <c r="O89">
-        <v>0.1832168616666666</v>
+        <v>0.1799513466666666</v>
       </c>
       <c r="P89">
-        <v>0.9271883605555551</v>
+        <v>0.9106628755555551</v>
       </c>
       <c r="Q89">
-        <v>2.617188360555556</v>
+        <v>2.600662875555555</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3055551637718029</v>
+        <v>0.3266592914450914</v>
       </c>
       <c r="T89">
-        <v>5.063111623944517</v>
+        <v>5.474470353389092</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.644903158827112</v>
+        <v>1.626211077476804</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.105331114973411</v>
+        <v>0.1055595586564876</v>
       </c>
       <c r="C90">
-        <v>-3.072262295547052</v>
+        <v>-3.337495619076996</v>
       </c>
       <c r="D90">
-        <v>11.85893770445295</v>
+        <v>11.81360438092301</v>
       </c>
       <c r="E90">
-        <v>1.251200000000001</v>
+        <v>1.4711</v>
       </c>
       <c r="F90">
-        <v>19.3512</v>
+        <v>19.5711</v>
       </c>
       <c r="G90">
         <v>4.42</v>
@@ -8655,28 +8655,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M90">
-        <v>1.741608</v>
+        <v>1.761399</v>
       </c>
       <c r="N90">
-        <v>1.090614222222222</v>
+        <v>1.070823222222222</v>
       </c>
       <c r="O90">
-        <v>0.1799513466666666</v>
+        <v>0.1766858316666666</v>
       </c>
       <c r="P90">
-        <v>0.9106628755555551</v>
+        <v>0.894137390555555</v>
       </c>
       <c r="Q90">
-        <v>2.600662875555555</v>
+        <v>2.584137390555555</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3266592914450914</v>
+        <v>0.351600533240796</v>
       </c>
       <c r="T90">
-        <v>5.474470353389092</v>
+        <v>5.960621579096316</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.626211077476804</v>
+        <v>1.607939042898413</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1055595586564876</v>
+        <v>0.1057880023395641</v>
       </c>
       <c r="C91">
-        <v>-3.337495619076996</v>
+        <v>-3.602383669852742</v>
       </c>
       <c r="D91">
-        <v>11.81360438092301</v>
+        <v>11.76861633014726</v>
       </c>
       <c r="E91">
-        <v>1.4711</v>
+        <v>1.691000000000003</v>
       </c>
       <c r="F91">
-        <v>19.5711</v>
+        <v>19.791</v>
       </c>
       <c r="G91">
         <v>4.42</v>
@@ -8737,28 +8737,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M91">
-        <v>1.761399</v>
+        <v>1.78119</v>
       </c>
       <c r="N91">
-        <v>1.070823222222222</v>
+        <v>1.051032222222221</v>
       </c>
       <c r="O91">
-        <v>0.1766858316666666</v>
+        <v>0.1734203166666665</v>
       </c>
       <c r="P91">
-        <v>0.894137390555555</v>
+        <v>0.8776119055555549</v>
       </c>
       <c r="Q91">
-        <v>2.584137390555555</v>
+        <v>2.567611905555555</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.351600533240796</v>
+        <v>0.3815300233956416</v>
       </c>
       <c r="T91">
-        <v>5.960621579096316</v>
+        <v>6.544003049944987</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.607939042898413</v>
+        <v>1.590073053532875</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1057880023395641</v>
+        <v>0.1060164460226407</v>
       </c>
       <c r="C92">
-        <v>-3.602383669852742</v>
+        <v>-3.866930377467522</v>
       </c>
       <c r="D92">
-        <v>11.76861633014726</v>
+        <v>11.72396962253248</v>
       </c>
       <c r="E92">
-        <v>1.691000000000003</v>
+        <v>1.910900000000002</v>
       </c>
       <c r="F92">
-        <v>19.791</v>
+        <v>20.0109</v>
       </c>
       <c r="G92">
         <v>4.42</v>
@@ -8819,28 +8819,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M92">
-        <v>1.78119</v>
+        <v>1.800981</v>
       </c>
       <c r="N92">
-        <v>1.051032222222221</v>
+        <v>1.031241222222222</v>
       </c>
       <c r="O92">
-        <v>0.1734203166666665</v>
+        <v>0.1701548016666666</v>
       </c>
       <c r="P92">
-        <v>0.8776119055555549</v>
+        <v>0.8610864205555551</v>
       </c>
       <c r="Q92">
-        <v>2.567611905555555</v>
+        <v>2.551086420555555</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3815300233956416</v>
+        <v>0.4181105113626751</v>
       </c>
       <c r="T92">
-        <v>6.544003049944987</v>
+        <v>7.257024847648917</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.590073053532875</v>
+        <v>1.572599723274272</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1060164460226407</v>
+        <v>0.1062448897057173</v>
       </c>
       <c r="C93">
-        <v>-3.866930377467522</v>
+        <v>-4.13113961210901</v>
       </c>
       <c r="D93">
-        <v>11.72396962253248</v>
+        <v>11.67966038789099</v>
       </c>
       <c r="E93">
-        <v>1.910900000000002</v>
+        <v>2.130800000000001</v>
       </c>
       <c r="F93">
-        <v>20.0109</v>
+        <v>20.2308</v>
       </c>
       <c r="G93">
         <v>4.42</v>
@@ -8901,28 +8901,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M93">
-        <v>1.800981</v>
+        <v>1.820772</v>
       </c>
       <c r="N93">
-        <v>1.031241222222222</v>
+        <v>1.011450222222222</v>
       </c>
       <c r="O93">
-        <v>0.1701548016666666</v>
+        <v>0.1668892866666666</v>
       </c>
       <c r="P93">
-        <v>0.8610864205555551</v>
+        <v>0.8445609355555551</v>
       </c>
       <c r="Q93">
-        <v>2.551086420555555</v>
+        <v>2.534560935555556</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4181105113626751</v>
+        <v>0.4638361213214671</v>
       </c>
       <c r="T93">
-        <v>7.257024847648917</v>
+        <v>8.148302094778833</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.572599723274272</v>
+        <v>1.555506248021291</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1062448897057173</v>
+        <v>0.1064733333887939</v>
       </c>
       <c r="C94">
-        <v>-4.13113961210901</v>
+        <v>-4.395015185677646</v>
       </c>
       <c r="D94">
-        <v>11.67966038789099</v>
+        <v>11.63568481432235</v>
       </c>
       <c r="E94">
-        <v>2.130800000000001</v>
+        <v>2.3507</v>
       </c>
       <c r="F94">
-        <v>20.2308</v>
+        <v>20.4507</v>
       </c>
       <c r="G94">
         <v>4.42</v>
@@ -8983,28 +8983,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M94">
-        <v>1.820772</v>
+        <v>1.840563</v>
       </c>
       <c r="N94">
-        <v>1.011450222222222</v>
+        <v>0.9916592222222218</v>
       </c>
       <c r="O94">
-        <v>0.1668892866666666</v>
+        <v>0.1636237716666666</v>
       </c>
       <c r="P94">
-        <v>0.8445609355555551</v>
+        <v>0.8280354505555552</v>
       </c>
       <c r="Q94">
-        <v>2.534560935555556</v>
+        <v>2.518035450555556</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4638361213214671</v>
+        <v>0.5226261912684851</v>
       </c>
       <c r="T94">
-        <v>8.148302094778833</v>
+        <v>9.294229983945863</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.555506248021291</v>
+        <v>1.538780374386653</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1064733333887939</v>
+        <v>0.1067017770718705</v>
       </c>
       <c r="C95">
-        <v>-4.395015185677646</v>
+        <v>-4.658560852879862</v>
       </c>
       <c r="D95">
-        <v>11.63568481432235</v>
+        <v>11.59203914712014</v>
       </c>
       <c r="E95">
-        <v>2.3507</v>
+        <v>2.570600000000002</v>
       </c>
       <c r="F95">
-        <v>20.4507</v>
+        <v>20.6706</v>
       </c>
       <c r="G95">
         <v>4.42</v>
@@ -9065,28 +9065,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M95">
-        <v>1.840563</v>
+        <v>1.860354</v>
       </c>
       <c r="N95">
-        <v>0.9916592222222218</v>
+        <v>0.9718682222222215</v>
       </c>
       <c r="O95">
-        <v>0.1636237716666666</v>
+        <v>0.1603582566666666</v>
       </c>
       <c r="P95">
-        <v>0.8280354505555552</v>
+        <v>0.8115099655555549</v>
       </c>
       <c r="Q95">
-        <v>2.518035450555556</v>
+        <v>2.501509965555555</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5226261912684851</v>
+        <v>0.6010129511978426</v>
       </c>
       <c r="T95">
-        <v>9.294229983945863</v>
+        <v>10.82213383616857</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.538780374386653</v>
+        <v>1.522410370403816</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1067017770718705</v>
+        <v>0.1069302207549471</v>
       </c>
       <c r="C96">
-        <v>-4.658560852879862</v>
+        <v>-4.921780312296702</v>
       </c>
       <c r="D96">
-        <v>11.59203914712014</v>
+        <v>11.5487196877033</v>
       </c>
       <c r="E96">
-        <v>2.570600000000002</v>
+        <v>2.790500000000002</v>
       </c>
       <c r="F96">
-        <v>20.6706</v>
+        <v>20.8905</v>
       </c>
       <c r="G96">
         <v>4.42</v>
@@ -9147,28 +9147,28 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M96">
-        <v>1.860354</v>
+        <v>1.880145</v>
       </c>
       <c r="N96">
-        <v>0.9718682222222215</v>
+        <v>0.9520772222222216</v>
       </c>
       <c r="O96">
-        <v>0.1603582566666666</v>
+        <v>0.1570927416666666</v>
       </c>
       <c r="P96">
-        <v>0.8115099655555549</v>
+        <v>0.794984480555555</v>
       </c>
       <c r="Q96">
-        <v>2.501509965555555</v>
+        <v>2.484984480555555</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6010129511978426</v>
+        <v>0.7107544150989433</v>
       </c>
       <c r="T96">
-        <v>10.82213383616857</v>
+        <v>12.96119922928037</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.522410370403816</v>
+        <v>1.506384998083776</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1069302207549471</v>
+        <v>0.1552289869976656</v>
       </c>
       <c r="C97">
-        <v>-4.921780312296702</v>
+        <v>-10.23894866780986</v>
       </c>
       <c r="D97">
-        <v>11.5487196877033</v>
+        <v>6.451451332190137</v>
       </c>
       <c r="E97">
-        <v>2.790500000000002</v>
+        <v>3.010400000000001</v>
       </c>
       <c r="F97">
-        <v>20.8905</v>
+        <v>21.1104</v>
       </c>
       <c r="G97">
         <v>4.42</v>
@@ -9229,45 +9229,45 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M97">
-        <v>1.880145</v>
+        <v>3.099006720000001</v>
       </c>
       <c r="N97">
-        <v>0.9520772222222216</v>
+        <v>-0.2667844977777789</v>
       </c>
       <c r="O97">
-        <v>0.1570927416666666</v>
+        <v>-0.04401944213333352</v>
       </c>
       <c r="P97">
-        <v>0.794984480555555</v>
+        <v>-0.2227650556444454</v>
       </c>
       <c r="Q97">
-        <v>2.484984480555555</v>
+        <v>1.467234944355555</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7107544150989433</v>
+        <v>0.8888078339533116</v>
       </c>
       <c r="T97">
-        <v>12.96119922928037</v>
+        <v>16.43179177340624</v>
       </c>
       <c r="U97">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.165</v>
+        <v>0.1507956286931403</v>
       </c>
       <c r="W97">
-        <v>0.07514999999999999</v>
+        <v>0.124663201707847</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.506384998083776</v>
+        <v>0.913912901170547</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1552289869976655</v>
+        <v>0.1562389869976656</v>
       </c>
       <c r="C98">
-        <v>-10.23894866780986</v>
+        <v>-10.51784926191754</v>
       </c>
       <c r="D98">
-        <v>6.451451332190139</v>
+        <v>6.392450738082462</v>
       </c>
       <c r="E98">
-        <v>3.010400000000001</v>
+        <v>3.2303</v>
       </c>
       <c r="F98">
-        <v>21.1104</v>
+        <v>21.3303</v>
       </c>
       <c r="G98">
         <v>4.42</v>
@@ -9311,37 +9311,37 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M98">
-        <v>3.099006720000001</v>
+        <v>3.13128804</v>
       </c>
       <c r="N98">
-        <v>-0.2667844977777789</v>
+        <v>-0.2990658177777785</v>
       </c>
       <c r="O98">
-        <v>-0.04401944213333352</v>
+        <v>-0.04934585993333346</v>
       </c>
       <c r="P98">
-        <v>-0.2227650556444454</v>
+        <v>-0.2497199578444451</v>
       </c>
       <c r="Q98">
-        <v>1.467234944355555</v>
+        <v>1.440280042155555</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8888078339533094</v>
+        <v>1.169810445271079</v>
       </c>
       <c r="T98">
-        <v>16.4317917734062</v>
+        <v>21.90905569787493</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1507956286931403</v>
+        <v>0.1492410345829017</v>
       </c>
       <c r="W98">
-        <v>0.124663201707847</v>
+        <v>0.12489141612323</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.913912901170547</v>
+        <v>0.9044911186842528</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1562389869976656</v>
+        <v>0.1572489869976656</v>
       </c>
       <c r="C99">
-        <v>-10.51784926191754</v>
+        <v>-10.79568047708057</v>
       </c>
       <c r="D99">
-        <v>6.392450738082462</v>
+        <v>6.334519522919434</v>
       </c>
       <c r="E99">
-        <v>3.2303</v>
+        <v>3.450199999999999</v>
       </c>
       <c r="F99">
-        <v>21.3303</v>
+        <v>21.5502</v>
       </c>
       <c r="G99">
         <v>4.42</v>
@@ -9393,37 +9393,37 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M99">
-        <v>3.13128804</v>
+        <v>3.16356936</v>
       </c>
       <c r="N99">
-        <v>-0.2990658177777785</v>
+        <v>-0.3313471377777786</v>
       </c>
       <c r="O99">
-        <v>-0.04934585993333346</v>
+        <v>-0.05467227773333347</v>
       </c>
       <c r="P99">
-        <v>-0.2497199578444451</v>
+        <v>-0.2766748600444451</v>
       </c>
       <c r="Q99">
-        <v>1.440280042155555</v>
+        <v>1.413325139955555</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.169810445271079</v>
+        <v>1.731815667906619</v>
       </c>
       <c r="T99">
-        <v>21.90905569787493</v>
+        <v>32.8635835468124</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1492410345829017</v>
+        <v>0.1477181668830762</v>
       </c>
       <c r="W99">
-        <v>0.12489141612323</v>
+        <v>0.1251149731015644</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9044911186842528</v>
+        <v>0.895261617473189</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1572489869976656</v>
+        <v>0.1582589869976655</v>
       </c>
       <c r="C100">
-        <v>-10.79568047708057</v>
+        <v>-11.07247112574239</v>
       </c>
       <c r="D100">
-        <v>6.334519522919434</v>
+        <v>6.277628874257614</v>
       </c>
       <c r="E100">
-        <v>3.450199999999999</v>
+        <v>3.670100000000001</v>
       </c>
       <c r="F100">
-        <v>21.5502</v>
+        <v>21.7701</v>
       </c>
       <c r="G100">
         <v>4.42</v>
@@ -9475,37 +9475,37 @@
         <v>2.832222222222222</v>
       </c>
       <c r="M100">
-        <v>3.16356936</v>
+        <v>3.195850680000001</v>
       </c>
       <c r="N100">
-        <v>-0.3313471377777786</v>
+        <v>-0.3636284577777791</v>
       </c>
       <c r="O100">
-        <v>-0.05467227773333347</v>
+        <v>-0.05999869553333355</v>
       </c>
       <c r="P100">
-        <v>-0.2766748600444451</v>
+        <v>-0.3036297622444455</v>
       </c>
       <c r="Q100">
-        <v>1.413325139955555</v>
+        <v>1.386370237755555</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.731815667906619</v>
+        <v>3.417831335813237</v>
       </c>
       <c r="T100">
-        <v>32.8635835468124</v>
+        <v>65.72716709362479</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1477181668830762</v>
+        <v>0.1462260641872875</v>
       </c>
       <c r="W100">
-        <v>0.1251149731015644</v>
+        <v>0.1253340137773062</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.895261617473189</v>
+        <v>0.8862185708320456</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1582589869976655</v>
-      </c>
-      <c r="C101">
-        <v>-11.07247112574239</v>
-      </c>
-      <c r="D101">
-        <v>6.277628874257614</v>
-      </c>
-      <c r="E101">
-        <v>3.670100000000001</v>
-      </c>
-      <c r="F101">
-        <v>21.7701</v>
-      </c>
-      <c r="G101">
-        <v>4.42</v>
-      </c>
-      <c r="H101">
-        <v>3.89</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.522222222222222</v>
-      </c>
-      <c r="K101">
-        <v>1.69</v>
-      </c>
-      <c r="L101">
-        <v>2.832222222222222</v>
-      </c>
-      <c r="M101">
-        <v>3.195850680000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.3636284577777791</v>
-      </c>
-      <c r="O101">
-        <v>-0.05999869553333355</v>
-      </c>
-      <c r="P101">
-        <v>-0.3036297622444455</v>
-      </c>
-      <c r="Q101">
-        <v>1.386370237755555</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.417831335813237</v>
-      </c>
-      <c r="T101">
-        <v>65.72716709362479</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1462260641872875</v>
-      </c>
-      <c r="W101">
-        <v>0.1253340137773062</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8862185708320456</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
